--- a/research/traditional_assets/database/data/czech_republic/czech_republic_tobacco.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_tobacco.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07439026162955983</v>
+        <v>0.07428537013246367</v>
       </c>
       <c r="C2">
-        <v>1905.957062588576</v>
+        <v>1889.108420839118</v>
       </c>
       <c r="D2">
-        <v>1640.457062588576</v>
+        <v>1642.667420839118</v>
       </c>
       <c r="E2">
-        <v>-13.1</v>
+        <v>5.958999999999998</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19.059</v>
       </c>
       <c r="G2">
         <v>265.5</v>
@@ -1451,28 +1451,28 @@
         <v>181.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9586676999999998</v>
       </c>
       <c r="N2">
-        <v>181.4</v>
+        <v>180.4413323</v>
       </c>
       <c r="O2">
-        <v>34.466</v>
+        <v>34.283853137</v>
       </c>
       <c r="P2">
-        <v>146.934</v>
+        <v>146.157479163</v>
       </c>
       <c r="Q2">
-        <v>171.334</v>
+        <v>170.557479163</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07439026162955983</v>
+        <v>0.0746241819519835</v>
       </c>
       <c r="T2">
-        <v>0.5572774141861078</v>
+        <v>0.5618369566658123</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>189.2209365142896</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07428537013246367</v>
+        <v>0.0741804786353675</v>
       </c>
       <c r="C3">
-        <v>1889.108420839118</v>
+        <v>1872.265743616958</v>
       </c>
       <c r="D3">
-        <v>1642.667420839118</v>
+        <v>1644.883743616958</v>
       </c>
       <c r="E3">
-        <v>5.958999999999998</v>
+        <v>25.01799999999999</v>
       </c>
       <c r="F3">
-        <v>19.059</v>
+        <v>38.11799999999999</v>
       </c>
       <c r="G3">
         <v>265.5</v>
@@ -1533,28 +1533,28 @@
         <v>181.4</v>
       </c>
       <c r="M3">
-        <v>0.9586676999999998</v>
+        <v>1.9173354</v>
       </c>
       <c r="N3">
-        <v>180.4413323</v>
+        <v>179.4826646</v>
       </c>
       <c r="O3">
-        <v>34.283853137</v>
+        <v>34.101706274</v>
       </c>
       <c r="P3">
-        <v>146.157479163</v>
+        <v>145.380958326</v>
       </c>
       <c r="Q3">
-        <v>170.557479163</v>
+        <v>169.780958326</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0746241819519835</v>
+        <v>0.07486287615853827</v>
       </c>
       <c r="T3">
-        <v>0.5618369566658123</v>
+        <v>0.5664895510328578</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>189.2209365142896</v>
+        <v>94.6104682571448</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0741804786353675</v>
+        <v>0.07407558713827134</v>
       </c>
       <c r="C4">
-        <v>1872.265743616958</v>
+        <v>1855.429055097128</v>
       </c>
       <c r="D4">
-        <v>1644.883743616958</v>
+        <v>1647.106055097128</v>
       </c>
       <c r="E4">
-        <v>25.01799999999999</v>
+        <v>44.07699999999999</v>
       </c>
       <c r="F4">
-        <v>38.11799999999999</v>
+        <v>57.17699999999999</v>
       </c>
       <c r="G4">
         <v>265.5</v>
@@ -1615,28 +1615,28 @@
         <v>181.4</v>
       </c>
       <c r="M4">
-        <v>1.9173354</v>
+        <v>2.876003099999999</v>
       </c>
       <c r="N4">
-        <v>179.4826646</v>
+        <v>178.5239969</v>
       </c>
       <c r="O4">
-        <v>34.101706274</v>
+        <v>33.919559411</v>
       </c>
       <c r="P4">
-        <v>145.380958326</v>
+        <v>144.604437489</v>
       </c>
       <c r="Q4">
-        <v>169.780958326</v>
+        <v>169.004437489</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07486287615853827</v>
+        <v>0.0751064918951251</v>
       </c>
       <c r="T4">
-        <v>0.5664895510328578</v>
+        <v>0.571238075180667</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>94.6104682571448</v>
+        <v>63.07364550476321</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07407558713827134</v>
+        <v>0.07397069564117519</v>
       </c>
       <c r="C5">
-        <v>1855.429055097128</v>
+        <v>1838.598379585478</v>
       </c>
       <c r="D5">
-        <v>1647.106055097128</v>
+        <v>1649.334379585478</v>
       </c>
       <c r="E5">
-        <v>44.07699999999999</v>
+        <v>63.13599999999999</v>
       </c>
       <c r="F5">
-        <v>57.17699999999999</v>
+        <v>76.23599999999999</v>
       </c>
       <c r="G5">
         <v>265.5</v>
@@ -1697,28 +1697,28 @@
         <v>181.4</v>
       </c>
       <c r="M5">
-        <v>2.876003099999999</v>
+        <v>3.834670799999999</v>
       </c>
       <c r="N5">
-        <v>178.5239969</v>
+        <v>177.5653292</v>
       </c>
       <c r="O5">
-        <v>33.919559411</v>
+        <v>33.737412548</v>
       </c>
       <c r="P5">
-        <v>144.604437489</v>
+        <v>143.827916652</v>
       </c>
       <c r="Q5">
-        <v>169.004437489</v>
+        <v>168.227916652</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0751064918951251</v>
+        <v>0.07535518295955748</v>
       </c>
       <c r="T5">
-        <v>0.571238075180667</v>
+        <v>0.5760855269148889</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.07364550476321</v>
+        <v>47.30523412857241</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07397069564117519</v>
+        <v>0.07386580414407901</v>
       </c>
       <c r="C6">
-        <v>1838.598379585478</v>
+        <v>1821.773741519571</v>
       </c>
       <c r="D6">
-        <v>1649.334379585478</v>
+        <v>1651.568741519571</v>
       </c>
       <c r="E6">
-        <v>63.13599999999999</v>
+        <v>82.19500000000001</v>
       </c>
       <c r="F6">
-        <v>76.23599999999999</v>
+        <v>95.295</v>
       </c>
       <c r="G6">
         <v>265.5</v>
@@ -1779,28 +1779,28 @@
         <v>181.4</v>
       </c>
       <c r="M6">
-        <v>3.834670799999999</v>
+        <v>4.7933385</v>
       </c>
       <c r="N6">
-        <v>177.5653292</v>
+        <v>176.6066615</v>
       </c>
       <c r="O6">
-        <v>33.737412548</v>
+        <v>33.555265685</v>
       </c>
       <c r="P6">
-        <v>143.827916652</v>
+        <v>143.051395815</v>
       </c>
       <c r="Q6">
-        <v>168.227916652</v>
+        <v>167.451395815</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07535518295955748</v>
+        <v>0.07560910962534632</v>
       </c>
       <c r="T6">
-        <v>0.5760855269148889</v>
+        <v>0.5810350302645682</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.30523412857241</v>
+        <v>37.84418730285792</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07386580414407901</v>
+        <v>0.07376091264698284</v>
       </c>
       <c r="C7">
-        <v>1821.773741519571</v>
+        <v>1804.955165469569</v>
       </c>
       <c r="D7">
-        <v>1651.568741519571</v>
+        <v>1653.809165469569</v>
       </c>
       <c r="E7">
-        <v>82.19500000000001</v>
+        <v>101.254</v>
       </c>
       <c r="F7">
-        <v>95.295</v>
+        <v>114.354</v>
       </c>
       <c r="G7">
         <v>265.5</v>
@@ -1861,28 +1861,28 @@
         <v>181.4</v>
       </c>
       <c r="M7">
-        <v>4.7933385</v>
+        <v>5.752006199999999</v>
       </c>
       <c r="N7">
-        <v>176.6066615</v>
+        <v>175.6479938</v>
       </c>
       <c r="O7">
-        <v>33.555265685</v>
+        <v>33.373118822</v>
       </c>
       <c r="P7">
-        <v>143.051395815</v>
+        <v>142.274874978</v>
       </c>
       <c r="Q7">
-        <v>167.451395815</v>
+        <v>166.674874978</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07560910962534632</v>
+        <v>0.07586843898615196</v>
       </c>
       <c r="T7">
-        <v>0.5810350302645682</v>
+        <v>0.5860898421961555</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.84418730285792</v>
+        <v>31.5368227523816</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07376091264698284</v>
+        <v>0.07365602114988669</v>
       </c>
       <c r="C8">
-        <v>1804.955165469569</v>
+        <v>1788.142676139139</v>
       </c>
       <c r="D8">
-        <v>1653.809165469569</v>
+        <v>1656.055676139139</v>
       </c>
       <c r="E8">
-        <v>101.254</v>
+        <v>120.313</v>
       </c>
       <c r="F8">
-        <v>114.354</v>
+        <v>133.413</v>
       </c>
       <c r="G8">
         <v>265.5</v>
@@ -1943,28 +1943,28 @@
         <v>181.4</v>
       </c>
       <c r="M8">
-        <v>5.752006199999999</v>
+        <v>6.710673899999999</v>
       </c>
       <c r="N8">
-        <v>175.6479938</v>
+        <v>174.6893261</v>
       </c>
       <c r="O8">
-        <v>33.373118822</v>
+        <v>33.190971959</v>
       </c>
       <c r="P8">
-        <v>142.274874978</v>
+        <v>141.498354141</v>
       </c>
       <c r="Q8">
-        <v>166.674874978</v>
+        <v>165.898354141</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07586843898615196</v>
+        <v>0.0761333453224588</v>
       </c>
       <c r="T8">
-        <v>0.5860898421961555</v>
+        <v>0.5912533597606802</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.5368227523816</v>
+        <v>27.03156235918423</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07365602114988669</v>
+        <v>0.07355112965279052</v>
       </c>
       <c r="C9">
-        <v>1788.142676139139</v>
+        <v>1771.336298366359</v>
       </c>
       <c r="D9">
-        <v>1656.055676139139</v>
+        <v>1658.308298366359</v>
       </c>
       <c r="E9">
-        <v>120.313</v>
+        <v>139.372</v>
       </c>
       <c r="F9">
-        <v>133.413</v>
+        <v>152.472</v>
       </c>
       <c r="G9">
         <v>265.5</v>
@@ -2025,28 +2025,28 @@
         <v>181.4</v>
       </c>
       <c r="M9">
-        <v>6.710673900000001</v>
+        <v>7.669341599999998</v>
       </c>
       <c r="N9">
-        <v>174.6893261</v>
+        <v>173.7306584</v>
       </c>
       <c r="O9">
-        <v>33.190971959</v>
+        <v>33.008825096</v>
       </c>
       <c r="P9">
-        <v>141.498354141</v>
+        <v>140.721833304</v>
       </c>
       <c r="Q9">
-        <v>165.898354141</v>
+        <v>165.121833304</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0761333453224588</v>
+        <v>0.07640401049216361</v>
       </c>
       <c r="T9">
-        <v>0.5912533597606802</v>
+        <v>0.5965291277070424</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.03156235918422</v>
+        <v>23.6526170642862</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07355112965279052</v>
+        <v>0.07344623815569436</v>
       </c>
       <c r="C10">
-        <v>1771.336298366359</v>
+        <v>1754.536057124633</v>
       </c>
       <c r="D10">
-        <v>1658.308298366359</v>
+        <v>1660.567057124633</v>
       </c>
       <c r="E10">
-        <v>139.372</v>
+        <v>158.431</v>
       </c>
       <c r="F10">
-        <v>152.472</v>
+        <v>171.531</v>
       </c>
       <c r="G10">
         <v>265.5</v>
@@ -2107,28 +2107,28 @@
         <v>181.4</v>
       </c>
       <c r="M10">
-        <v>7.669341599999998</v>
+        <v>8.628009299999999</v>
       </c>
       <c r="N10">
-        <v>173.7306584</v>
+        <v>172.7719907</v>
       </c>
       <c r="O10">
-        <v>33.008825096</v>
+        <v>32.826678233</v>
       </c>
       <c r="P10">
-        <v>140.721833304</v>
+        <v>139.945312467</v>
       </c>
       <c r="Q10">
-        <v>165.121833304</v>
+        <v>164.345312467</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07640401049216361</v>
+        <v>0.07668062434691687</v>
       </c>
       <c r="T10">
-        <v>0.5965291277070424</v>
+        <v>0.6019208465972805</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.6526170642862</v>
+        <v>21.02454850158773</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07344623815569436</v>
+        <v>0.07334134665859819</v>
       </c>
       <c r="C11">
-        <v>1754.536057124633</v>
+        <v>1737.741977523614</v>
       </c>
       <c r="D11">
-        <v>1660.567057124633</v>
+        <v>1662.831977523614</v>
       </c>
       <c r="E11">
-        <v>158.431</v>
+        <v>177.49</v>
       </c>
       <c r="F11">
-        <v>171.531</v>
+        <v>190.59</v>
       </c>
       <c r="G11">
         <v>265.5</v>
@@ -2189,28 +2189,28 @@
         <v>181.4</v>
       </c>
       <c r="M11">
-        <v>8.628009299999999</v>
+        <v>9.586676999999998</v>
       </c>
       <c r="N11">
-        <v>172.7719907</v>
+        <v>171.813323</v>
       </c>
       <c r="O11">
-        <v>32.826678233</v>
+        <v>32.64453137</v>
       </c>
       <c r="P11">
-        <v>139.945312467</v>
+        <v>139.16879163</v>
       </c>
       <c r="Q11">
-        <v>164.345312467</v>
+        <v>163.56879163</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07668062434691687</v>
+        <v>0.07696338517622021</v>
       </c>
       <c r="T11">
-        <v>0.6019208465972805</v>
+        <v>0.6074323814628575</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.02454850158773</v>
+        <v>18.92209365142896</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07334134665859819</v>
+        <v>0.07323645516150204</v>
       </c>
       <c r="C12">
-        <v>1737.741977523614</v>
+        <v>1720.954084810134</v>
       </c>
       <c r="D12">
-        <v>1662.831977523614</v>
+        <v>1665.103084810134</v>
       </c>
       <c r="E12">
-        <v>177.49</v>
+        <v>196.549</v>
       </c>
       <c r="F12">
-        <v>190.59</v>
+        <v>209.649</v>
       </c>
       <c r="G12">
         <v>265.5</v>
@@ -2271,28 +2271,28 @@
         <v>181.4</v>
       </c>
       <c r="M12">
-        <v>9.586677</v>
+        <v>10.5453447</v>
       </c>
       <c r="N12">
-        <v>171.813323</v>
+        <v>170.8546553</v>
       </c>
       <c r="O12">
-        <v>32.64453137</v>
+        <v>32.462384507</v>
       </c>
       <c r="P12">
-        <v>139.16879163</v>
+        <v>138.392270793</v>
       </c>
       <c r="Q12">
-        <v>163.56879163</v>
+        <v>162.792270793</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07696338517622021</v>
+        <v>0.07725250018146296</v>
       </c>
       <c r="T12">
-        <v>0.6074323814628575</v>
+        <v>0.6130677710445147</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.92209365142896</v>
+        <v>17.20190331948088</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07323645516150204</v>
+        <v>0.07313156366440586</v>
       </c>
       <c r="C13">
-        <v>1720.954084810134</v>
+        <v>1704.172404369147</v>
       </c>
       <c r="D13">
-        <v>1665.103084810134</v>
+        <v>1667.380404369147</v>
       </c>
       <c r="E13">
-        <v>196.549</v>
+        <v>215.608</v>
       </c>
       <c r="F13">
-        <v>209.649</v>
+        <v>228.708</v>
       </c>
       <c r="G13">
         <v>265.5</v>
@@ -2353,28 +2353,28 @@
         <v>181.4</v>
       </c>
       <c r="M13">
-        <v>10.5453447</v>
+        <v>11.5040124</v>
       </c>
       <c r="N13">
-        <v>170.8546553</v>
+        <v>169.8959876</v>
       </c>
       <c r="O13">
-        <v>32.462384507</v>
+        <v>32.280237644</v>
       </c>
       <c r="P13">
-        <v>138.392270793</v>
+        <v>137.615749956</v>
       </c>
       <c r="Q13">
-        <v>162.792270793</v>
+        <v>162.015749956</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07725250018146296</v>
+        <v>0.07754818598227939</v>
       </c>
       <c r="T13">
-        <v>0.6130677710445147</v>
+        <v>0.6188312376621187</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.20190331948088</v>
+        <v>15.7684113761908</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07313156366440586</v>
+        <v>0.07302667216730969</v>
       </c>
       <c r="C14">
-        <v>1704.172404369147</v>
+        <v>1687.396961724664</v>
       </c>
       <c r="D14">
-        <v>1667.380404369147</v>
+        <v>1669.663961724664</v>
       </c>
       <c r="E14">
-        <v>215.608</v>
+        <v>234.667</v>
       </c>
       <c r="F14">
-        <v>228.708</v>
+        <v>247.767</v>
       </c>
       <c r="G14">
         <v>265.5</v>
@@ -2435,28 +2435,28 @@
         <v>181.4</v>
       </c>
       <c r="M14">
-        <v>11.5040124</v>
+        <v>12.4626801</v>
       </c>
       <c r="N14">
-        <v>169.8959876</v>
+        <v>168.9373199</v>
       </c>
       <c r="O14">
-        <v>32.280237644</v>
+        <v>32.098090781</v>
       </c>
       <c r="P14">
-        <v>137.615749956</v>
+        <v>136.839229119</v>
       </c>
       <c r="Q14">
-        <v>162.015749956</v>
+        <v>161.239229119</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07754818598227939</v>
+        <v>0.07785066915782723</v>
       </c>
       <c r="T14">
-        <v>0.6188312376621187</v>
+        <v>0.6247271977651849</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.7684113761908</v>
+        <v>14.55545665494535</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07302667216730969</v>
+        <v>0.07292178067021354</v>
       </c>
       <c r="C15">
-        <v>1687.396961724664</v>
+        <v>1670.627782540718</v>
       </c>
       <c r="D15">
-        <v>1669.663961724664</v>
+        <v>1671.953782540718</v>
       </c>
       <c r="E15">
-        <v>234.667</v>
+        <v>253.726</v>
       </c>
       <c r="F15">
-        <v>247.767</v>
+        <v>266.826</v>
       </c>
       <c r="G15">
         <v>265.5</v>
@@ -2517,28 +2517,28 @@
         <v>181.4</v>
       </c>
       <c r="M15">
-        <v>12.4626801</v>
+        <v>13.4213478</v>
       </c>
       <c r="N15">
-        <v>168.9373199</v>
+        <v>167.9786522</v>
       </c>
       <c r="O15">
-        <v>32.098090781</v>
+        <v>31.915943918</v>
       </c>
       <c r="P15">
-        <v>136.839229119</v>
+        <v>136.062708282</v>
       </c>
       <c r="Q15">
-        <v>161.239229119</v>
+        <v>160.462708282</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07785066915782723</v>
+        <v>0.0781601868258297</v>
       </c>
       <c r="T15">
-        <v>0.6247271977651849</v>
+        <v>0.6307602732194852</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.55545665494535</v>
+        <v>13.51578117959211</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07292178067021354</v>
+        <v>0.07299913917311737</v>
       </c>
       <c r="C16">
-        <v>1670.627782540718</v>
+        <v>1649.879410021511</v>
       </c>
       <c r="D16">
-        <v>1671.953782540718</v>
+        <v>1670.264410021511</v>
       </c>
       <c r="E16">
-        <v>253.726</v>
+        <v>272.785</v>
       </c>
       <c r="F16">
-        <v>266.826</v>
+        <v>285.885</v>
       </c>
       <c r="G16">
         <v>265.5</v>
@@ -2599,45 +2599,45 @@
         <v>181.4</v>
       </c>
       <c r="M16">
-        <v>13.4213478</v>
+        <v>14.808843</v>
       </c>
       <c r="N16">
-        <v>167.9786522</v>
+        <v>166.591157</v>
       </c>
       <c r="O16">
-        <v>31.915943918</v>
+        <v>31.65231983</v>
       </c>
       <c r="P16">
-        <v>136.062708282</v>
+        <v>134.93883717</v>
       </c>
       <c r="Q16">
-        <v>160.462708282</v>
+        <v>159.33883717</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0781601868258297</v>
+        <v>0.07847698726249103</v>
       </c>
       <c r="T16">
-        <v>0.6307602732194852</v>
+        <v>0.6369353033903573</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.19</v>
       </c>
       <c r="W16">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.51578117959211</v>
+        <v>12.24943771772042</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07299913917311737</v>
+        <v>0.07290639767602121</v>
       </c>
       <c r="C17">
-        <v>1649.879410021511</v>
+        <v>1632.846127283259</v>
       </c>
       <c r="D17">
-        <v>1670.264410021511</v>
+        <v>1672.290127283258</v>
       </c>
       <c r="E17">
-        <v>272.785</v>
+        <v>291.8439999999999</v>
       </c>
       <c r="F17">
-        <v>285.885</v>
+        <v>304.944</v>
       </c>
       <c r="G17">
         <v>265.5</v>
@@ -2681,28 +2681,28 @@
         <v>181.4</v>
       </c>
       <c r="M17">
-        <v>14.808843</v>
+        <v>15.7960992</v>
       </c>
       <c r="N17">
-        <v>166.591157</v>
+        <v>165.6039008</v>
       </c>
       <c r="O17">
-        <v>31.65231983</v>
+        <v>31.46474115200001</v>
       </c>
       <c r="P17">
-        <v>134.93883717</v>
+        <v>134.139159648</v>
       </c>
       <c r="Q17">
-        <v>159.33883717</v>
+        <v>158.539159648</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07847698726249103</v>
+        <v>0.07880133056669192</v>
       </c>
       <c r="T17">
-        <v>0.6369353033903573</v>
+        <v>0.6432573580891073</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.24943771772042</v>
+        <v>11.4838478603629</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07290639767602121</v>
+        <v>0.07281365617892505</v>
       </c>
       <c r="C18">
-        <v>1632.846127283259</v>
+        <v>1615.817764141274</v>
       </c>
       <c r="D18">
-        <v>1672.290127283258</v>
+        <v>1674.320764141274</v>
       </c>
       <c r="E18">
-        <v>291.8439999999999</v>
+        <v>310.903</v>
       </c>
       <c r="F18">
-        <v>304.944</v>
+        <v>324.003</v>
       </c>
       <c r="G18">
         <v>265.5</v>
@@ -2763,28 +2763,28 @@
         <v>181.4</v>
       </c>
       <c r="M18">
-        <v>15.7960992</v>
+        <v>16.7833554</v>
       </c>
       <c r="N18">
-        <v>165.6039008</v>
+        <v>164.6166446</v>
       </c>
       <c r="O18">
-        <v>31.46474115200001</v>
+        <v>31.277162474</v>
       </c>
       <c r="P18">
-        <v>134.139159648</v>
+        <v>133.339482126</v>
       </c>
       <c r="Q18">
-        <v>158.539159648</v>
+        <v>157.739482126</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07880133056669192</v>
+        <v>0.07913348937219886</v>
       </c>
       <c r="T18">
-        <v>0.6432573580891073</v>
+        <v>0.649731751455297</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.4838478603629</v>
+        <v>10.80832739798861</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07281365617892505</v>
+        <v>0.07272091468182888</v>
       </c>
       <c r="C19">
-        <v>1615.817764141274</v>
+        <v>1598.794338538723</v>
       </c>
       <c r="D19">
-        <v>1674.320764141274</v>
+        <v>1676.356338538724</v>
       </c>
       <c r="E19">
-        <v>310.903</v>
+        <v>329.962</v>
       </c>
       <c r="F19">
-        <v>324.003</v>
+        <v>343.062</v>
       </c>
       <c r="G19">
         <v>265.5</v>
@@ -2845,28 +2845,28 @@
         <v>181.4</v>
       </c>
       <c r="M19">
-        <v>16.7833554</v>
+        <v>17.7706116</v>
       </c>
       <c r="N19">
-        <v>164.6166446</v>
+        <v>163.6293884</v>
       </c>
       <c r="O19">
-        <v>31.277162474</v>
+        <v>31.089583796</v>
       </c>
       <c r="P19">
-        <v>133.339482126</v>
+        <v>132.539804604</v>
       </c>
       <c r="Q19">
-        <v>157.739482126</v>
+        <v>156.939804604</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07913348937219886</v>
+        <v>0.07947374961198644</v>
       </c>
       <c r="T19">
-        <v>0.649731751455297</v>
+        <v>0.6563640568548084</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.80832739798861</v>
+        <v>10.20786476476702</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0727209146818289</v>
+        <v>0.07288980318473272</v>
       </c>
       <c r="C20">
-        <v>1598.794338538724</v>
+        <v>1576.032112824232</v>
       </c>
       <c r="D20">
-        <v>1676.356338538724</v>
+        <v>1672.653112824232</v>
       </c>
       <c r="E20">
-        <v>329.9619999999999</v>
+        <v>349.021</v>
       </c>
       <c r="F20">
-        <v>343.062</v>
+        <v>362.121</v>
       </c>
       <c r="G20">
         <v>265.5</v>
@@ -2927,45 +2927,45 @@
         <v>181.4</v>
       </c>
       <c r="M20">
-        <v>17.7706116</v>
+        <v>19.3734735</v>
       </c>
       <c r="N20">
-        <v>163.6293884</v>
+        <v>162.0265265</v>
       </c>
       <c r="O20">
-        <v>31.089583796</v>
+        <v>30.78504003500001</v>
       </c>
       <c r="P20">
-        <v>132.539804604</v>
+        <v>131.241486465</v>
       </c>
       <c r="Q20">
-        <v>156.939804604</v>
+        <v>155.641486465</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07947374961198644</v>
+        <v>0.0798224113391762</v>
       </c>
       <c r="T20">
-        <v>0.6563640568548084</v>
+        <v>0.6631601228814682</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.19</v>
       </c>
       <c r="W20">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.20786476476702</v>
+        <v>9.363318353830563</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07288980318473272</v>
+        <v>0.07281083168763655</v>
       </c>
       <c r="C21">
-        <v>1576.032112824232</v>
+        <v>1558.702685645899</v>
       </c>
       <c r="D21">
-        <v>1672.653112824232</v>
+        <v>1674.3826856459</v>
       </c>
       <c r="E21">
-        <v>349.021</v>
+        <v>368.08</v>
       </c>
       <c r="F21">
-        <v>362.121</v>
+        <v>381.18</v>
       </c>
       <c r="G21">
         <v>265.5</v>
@@ -3009,28 +3009,28 @@
         <v>181.4</v>
       </c>
       <c r="M21">
-        <v>19.3734735</v>
+        <v>20.39313</v>
       </c>
       <c r="N21">
-        <v>162.0265265</v>
+        <v>161.00687</v>
       </c>
       <c r="O21">
-        <v>30.78504003500001</v>
+        <v>30.5913053</v>
       </c>
       <c r="P21">
-        <v>131.241486465</v>
+        <v>130.4155647</v>
       </c>
       <c r="Q21">
-        <v>155.641486465</v>
+        <v>154.8155647</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0798224113391762</v>
+        <v>0.08017978960954569</v>
       </c>
       <c r="T21">
-        <v>0.6631601228814682</v>
+        <v>0.6701260905587947</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.363318353830563</v>
+        <v>8.895152436139032</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07281083168763655</v>
+        <v>0.07273186019054041</v>
       </c>
       <c r="C22">
-        <v>1558.702685645899</v>
+        <v>1541.376839028944</v>
       </c>
       <c r="D22">
-        <v>1674.3826856459</v>
+        <v>1676.115839028944</v>
       </c>
       <c r="E22">
-        <v>368.08</v>
+        <v>387.139</v>
       </c>
       <c r="F22">
-        <v>381.18</v>
+        <v>400.239</v>
       </c>
       <c r="G22">
         <v>265.5</v>
@@ -3091,28 +3091,28 @@
         <v>181.4</v>
       </c>
       <c r="M22">
-        <v>20.39313</v>
+        <v>21.4127865</v>
       </c>
       <c r="N22">
-        <v>161.00687</v>
+        <v>159.9872135</v>
       </c>
       <c r="O22">
-        <v>30.5913053</v>
+        <v>30.397570565</v>
       </c>
       <c r="P22">
-        <v>130.4155647</v>
+        <v>129.589642935</v>
       </c>
       <c r="Q22">
-        <v>154.8155647</v>
+        <v>153.989642935</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08017978960954569</v>
+        <v>0.0805462154310638</v>
       </c>
       <c r="T22">
-        <v>0.6701260905587947</v>
+        <v>0.6772684118482052</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.895152436139032</v>
+        <v>8.47157374870384</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0727318601905404</v>
+        <v>0.07265288869344425</v>
       </c>
       <c r="C23">
-        <v>1541.376839028944</v>
+        <v>1524.054584103603</v>
       </c>
       <c r="D23">
-        <v>1676.115839028944</v>
+        <v>1677.852584103603</v>
       </c>
       <c r="E23">
-        <v>387.139</v>
+        <v>406.1979999999999</v>
       </c>
       <c r="F23">
-        <v>400.239</v>
+        <v>419.2979999999999</v>
       </c>
       <c r="G23">
         <v>265.5</v>
@@ -3173,28 +3173,28 @@
         <v>181.4</v>
       </c>
       <c r="M23">
-        <v>21.4127865</v>
+        <v>22.432443</v>
       </c>
       <c r="N23">
-        <v>159.9872135</v>
+        <v>158.967557</v>
       </c>
       <c r="O23">
-        <v>30.397570565</v>
+        <v>30.20383583</v>
       </c>
       <c r="P23">
-        <v>129.589642935</v>
+        <v>128.76372117</v>
       </c>
       <c r="Q23">
-        <v>153.989642935</v>
+        <v>153.16372117</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0805462154310638</v>
+        <v>0.08092203678646696</v>
       </c>
       <c r="T23">
-        <v>0.6772684118482052</v>
+        <v>0.6845938695809339</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.471573748703841</v>
+        <v>8.086502214671849</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07265288869344425</v>
+        <v>0.07257391719634808</v>
       </c>
       <c r="C24">
-        <v>1524.054584103603</v>
+        <v>1506.735932046292</v>
       </c>
       <c r="D24">
-        <v>1677.852584103603</v>
+        <v>1679.592932046292</v>
       </c>
       <c r="E24">
-        <v>406.1979999999999</v>
+        <v>425.2569999999999</v>
       </c>
       <c r="F24">
-        <v>419.2979999999999</v>
+        <v>438.357</v>
       </c>
       <c r="G24">
         <v>265.5</v>
@@ -3255,28 +3255,28 @@
         <v>181.4</v>
       </c>
       <c r="M24">
-        <v>22.432443</v>
+        <v>23.4520995</v>
       </c>
       <c r="N24">
-        <v>158.967557</v>
+        <v>157.9479005</v>
       </c>
       <c r="O24">
-        <v>30.20383583</v>
+        <v>30.010101095</v>
       </c>
       <c r="P24">
-        <v>128.76372117</v>
+        <v>127.937799405</v>
       </c>
       <c r="Q24">
-        <v>153.16372117</v>
+        <v>152.337799405</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08092203678646696</v>
+        <v>0.08130761973551698</v>
       </c>
       <c r="T24">
-        <v>0.6845938695809339</v>
+        <v>0.6921095989430842</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.086502214671849</v>
+        <v>7.734915161860029</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07257391719634808</v>
+        <v>0.07265046569925192</v>
       </c>
       <c r="C25">
-        <v>1506.735932046292</v>
+        <v>1485.989927621861</v>
       </c>
       <c r="D25">
-        <v>1679.592932046292</v>
+        <v>1677.905927621861</v>
       </c>
       <c r="E25">
-        <v>425.2569999999999</v>
+        <v>444.316</v>
       </c>
       <c r="F25">
-        <v>438.357</v>
+        <v>457.416</v>
       </c>
       <c r="G25">
         <v>265.5</v>
@@ -3337,45 +3337,45 @@
         <v>181.4</v>
       </c>
       <c r="M25">
-        <v>23.4520995</v>
+        <v>24.8376888</v>
       </c>
       <c r="N25">
-        <v>157.9479005</v>
+        <v>156.5623112</v>
       </c>
       <c r="O25">
-        <v>30.010101095</v>
+        <v>29.746839128</v>
       </c>
       <c r="P25">
-        <v>127.937799405</v>
+        <v>126.815472072</v>
       </c>
       <c r="Q25">
-        <v>152.337799405</v>
+        <v>151.215472072</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08130761973551698</v>
+        <v>0.08170334960427883</v>
       </c>
       <c r="T25">
-        <v>0.6921095989430842</v>
+        <v>0.6998231106568701</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.19</v>
       </c>
       <c r="W25">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.734915161860029</v>
+        <v>7.303417055454855</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07265046569925192</v>
+        <v>0.07257797420215574</v>
       </c>
       <c r="C26">
-        <v>1485.989927621861</v>
+        <v>1468.528437115146</v>
       </c>
       <c r="D26">
-        <v>1677.905927621861</v>
+        <v>1679.503437115146</v>
       </c>
       <c r="E26">
-        <v>444.3159999999999</v>
+        <v>463.3749999999999</v>
       </c>
       <c r="F26">
-        <v>457.4159999999999</v>
+        <v>476.475</v>
       </c>
       <c r="G26">
         <v>265.5</v>
@@ -3419,28 +3419,28 @@
         <v>181.4</v>
       </c>
       <c r="M26">
-        <v>24.8376888</v>
+        <v>25.8725925</v>
       </c>
       <c r="N26">
-        <v>156.5623112</v>
+        <v>155.5274075</v>
       </c>
       <c r="O26">
-        <v>29.746839128</v>
+        <v>29.550207425</v>
       </c>
       <c r="P26">
-        <v>126.815472072</v>
+        <v>125.977200075</v>
       </c>
       <c r="Q26">
-        <v>151.215472072</v>
+        <v>150.377200075</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08170334960427883</v>
+        <v>0.08210963226954099</v>
       </c>
       <c r="T26">
-        <v>0.6998231106568701</v>
+        <v>0.7077423160163568</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.303417055454855</v>
+        <v>7.01128037323666</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07257797420215574</v>
+        <v>0.07250548270505958</v>
       </c>
       <c r="C27">
-        <v>1468.528437115146</v>
+        <v>1451.069991437835</v>
       </c>
       <c r="D27">
-        <v>1679.503437115146</v>
+        <v>1681.103991437835</v>
       </c>
       <c r="E27">
-        <v>463.3749999999999</v>
+        <v>482.434</v>
       </c>
       <c r="F27">
-        <v>476.475</v>
+        <v>495.534</v>
       </c>
       <c r="G27">
         <v>265.5</v>
@@ -3501,28 +3501,28 @@
         <v>181.4</v>
       </c>
       <c r="M27">
-        <v>25.8725925</v>
+        <v>26.9074962</v>
       </c>
       <c r="N27">
-        <v>155.5274075</v>
+        <v>154.4925038</v>
       </c>
       <c r="O27">
-        <v>29.550207425</v>
+        <v>29.353575722</v>
       </c>
       <c r="P27">
-        <v>125.977200075</v>
+        <v>125.138928078</v>
       </c>
       <c r="Q27">
-        <v>150.377200075</v>
+        <v>149.538928078</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08210963226954099</v>
+        <v>0.08252689554737781</v>
       </c>
       <c r="T27">
-        <v>0.7077423160163568</v>
+        <v>0.7158755539531272</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.01128037323666</v>
+        <v>6.741615743496788</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07250548270505958</v>
+        <v>0.07243299120796341</v>
       </c>
       <c r="C28">
-        <v>1451.069991437835</v>
+        <v>1433.614599303331</v>
       </c>
       <c r="D28">
-        <v>1681.103991437835</v>
+        <v>1682.707599303331</v>
       </c>
       <c r="E28">
-        <v>482.434</v>
+        <v>501.4929999999999</v>
       </c>
       <c r="F28">
-        <v>495.534</v>
+        <v>514.593</v>
       </c>
       <c r="G28">
         <v>265.5</v>
@@ -3583,28 +3583,28 @@
         <v>181.4</v>
       </c>
       <c r="M28">
-        <v>26.9074962</v>
+        <v>27.9423999</v>
       </c>
       <c r="N28">
-        <v>154.4925038</v>
+        <v>153.4576001</v>
       </c>
       <c r="O28">
-        <v>29.353575722</v>
+        <v>29.156944019</v>
       </c>
       <c r="P28">
-        <v>125.138928078</v>
+        <v>124.300656081</v>
       </c>
       <c r="Q28">
-        <v>149.538928078</v>
+        <v>148.700656081</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08252689554737781</v>
+        <v>0.0829555906958403</v>
       </c>
       <c r="T28">
-        <v>0.7158755539531272</v>
+        <v>0.7242316203265211</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.741615743496788</v>
+        <v>6.491926271515426</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07243299120796341</v>
+        <v>0.07236049971086725</v>
       </c>
       <c r="C29">
-        <v>1433.614599303331</v>
+        <v>1416.162269458317</v>
       </c>
       <c r="D29">
-        <v>1682.707599303331</v>
+        <v>1684.314269458318</v>
       </c>
       <c r="E29">
-        <v>501.4929999999999</v>
+        <v>520.552</v>
       </c>
       <c r="F29">
-        <v>514.593</v>
+        <v>533.652</v>
       </c>
       <c r="G29">
         <v>265.5</v>
@@ -3665,28 +3665,28 @@
         <v>181.4</v>
       </c>
       <c r="M29">
-        <v>27.9423999</v>
+        <v>28.9773036</v>
       </c>
       <c r="N29">
-        <v>153.4576001</v>
+        <v>152.4226964</v>
       </c>
       <c r="O29">
-        <v>29.156944019</v>
+        <v>28.960312316</v>
       </c>
       <c r="P29">
-        <v>124.300656081</v>
+        <v>123.462384084</v>
       </c>
       <c r="Q29">
-        <v>148.700656081</v>
+        <v>147.862384084</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0829555906958403</v>
+        <v>0.08339619404287117</v>
       </c>
       <c r="T29">
-        <v>0.7242316203265211</v>
+        <v>0.7328197996547317</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.491926271515426</v>
+        <v>6.260071761818446</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07236049971086725</v>
+        <v>0.07252290821377108</v>
       </c>
       <c r="C30">
-        <v>1416.162269458317</v>
+        <v>1393.507971676334</v>
       </c>
       <c r="D30">
-        <v>1684.314269458318</v>
+        <v>1680.718971676334</v>
       </c>
       <c r="E30">
-        <v>520.552</v>
+        <v>539.611</v>
       </c>
       <c r="F30">
-        <v>533.652</v>
+        <v>552.711</v>
       </c>
       <c r="G30">
         <v>265.5</v>
@@ -3747,45 +3747,45 @@
         <v>181.4</v>
       </c>
       <c r="M30">
-        <v>28.9773036</v>
+        <v>30.5649183</v>
       </c>
       <c r="N30">
-        <v>152.4226964</v>
+        <v>150.8350817</v>
       </c>
       <c r="O30">
-        <v>28.960312316</v>
+        <v>28.658665523</v>
       </c>
       <c r="P30">
-        <v>123.462384084</v>
+        <v>122.176416177</v>
       </c>
       <c r="Q30">
-        <v>147.862384084</v>
+        <v>146.576416177</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08339619404287117</v>
+        <v>0.08384920875179026</v>
       </c>
       <c r="T30">
-        <v>0.7328197996547317</v>
+        <v>0.741649899527399</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.19</v>
       </c>
       <c r="W30">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.260071761818446</v>
+        <v>5.93490871526393</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07252290821377107</v>
+        <v>0.07245851671667491</v>
       </c>
       <c r="C31">
-        <v>1393.507971676334</v>
+        <v>1375.872592414324</v>
       </c>
       <c r="D31">
-        <v>1680.718971676334</v>
+        <v>1682.142592414324</v>
       </c>
       <c r="E31">
-        <v>539.6109999999999</v>
+        <v>558.67</v>
       </c>
       <c r="F31">
-        <v>552.7109999999999</v>
+        <v>571.77</v>
       </c>
       <c r="G31">
         <v>265.5</v>
@@ -3829,28 +3829,28 @@
         <v>181.4</v>
       </c>
       <c r="M31">
-        <v>30.5649183</v>
+        <v>31.618881</v>
       </c>
       <c r="N31">
-        <v>150.8350817</v>
+        <v>149.781119</v>
       </c>
       <c r="O31">
-        <v>28.658665523</v>
+        <v>28.45841261</v>
       </c>
       <c r="P31">
-        <v>122.176416177</v>
+        <v>121.32270639</v>
       </c>
       <c r="Q31">
-        <v>146.576416177</v>
+        <v>145.72270639</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08384920875179025</v>
+        <v>0.08431516673810703</v>
       </c>
       <c r="T31">
-        <v>0.7416498995273989</v>
+        <v>0.7507322879678566</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.934908715263932</v>
+        <v>5.737078424755132</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07245851671667491</v>
+        <v>0.07239412521957875</v>
       </c>
       <c r="C32">
-        <v>1375.872592414324</v>
+        <v>1358.239626898062</v>
       </c>
       <c r="D32">
-        <v>1682.142592414324</v>
+        <v>1683.568626898062</v>
       </c>
       <c r="E32">
-        <v>558.67</v>
+        <v>577.7289999999999</v>
       </c>
       <c r="F32">
-        <v>571.77</v>
+        <v>590.829</v>
       </c>
       <c r="G32">
         <v>265.5</v>
@@ -3911,28 +3911,28 @@
         <v>181.4</v>
       </c>
       <c r="M32">
-        <v>31.618881</v>
+        <v>32.6728437</v>
       </c>
       <c r="N32">
-        <v>149.781119</v>
+        <v>148.7271563</v>
       </c>
       <c r="O32">
-        <v>28.45841261</v>
+        <v>28.258159697</v>
       </c>
       <c r="P32">
-        <v>121.32270639</v>
+        <v>120.468996603</v>
       </c>
       <c r="Q32">
-        <v>145.72270639</v>
+        <v>144.868996603</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08431516673810703</v>
+        <v>0.08479463075301269</v>
       </c>
       <c r="T32">
-        <v>0.7507322879678566</v>
+        <v>0.7600779340442696</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.737078424755132</v>
+        <v>5.55201137879529</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07239412521957875</v>
+        <v>0.07232973372248259</v>
       </c>
       <c r="C33">
-        <v>1358.239626898062</v>
+        <v>1340.609081271505</v>
       </c>
       <c r="D33">
-        <v>1683.568626898062</v>
+        <v>1684.997081271505</v>
       </c>
       <c r="E33">
-        <v>577.7289999999999</v>
+        <v>596.7879999999999</v>
       </c>
       <c r="F33">
-        <v>590.829</v>
+        <v>609.8879999999999</v>
       </c>
       <c r="G33">
         <v>265.5</v>
@@ -3993,28 +3993,28 @@
         <v>181.4</v>
       </c>
       <c r="M33">
-        <v>32.6728437</v>
+        <v>33.72680639999999</v>
       </c>
       <c r="N33">
-        <v>148.7271563</v>
+        <v>147.6731936</v>
       </c>
       <c r="O33">
-        <v>28.258159697</v>
+        <v>28.057906784</v>
       </c>
       <c r="P33">
-        <v>120.468996603</v>
+        <v>119.615286816</v>
       </c>
       <c r="Q33">
-        <v>144.868996603</v>
+        <v>144.015286816</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08479463075301269</v>
+        <v>0.08528819665070969</v>
       </c>
       <c r="T33">
-        <v>0.7600779340442696</v>
+        <v>0.7696984520641066</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.55201137879529</v>
+        <v>5.378511023207938</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07232973372248259</v>
+        <v>0.07226534222538643</v>
       </c>
       <c r="C34">
-        <v>1340.609081271505</v>
+        <v>1322.980961699483</v>
       </c>
       <c r="D34">
-        <v>1684.997081271505</v>
+        <v>1686.427961699483</v>
       </c>
       <c r="E34">
-        <v>596.7879999999999</v>
+        <v>615.847</v>
       </c>
       <c r="F34">
-        <v>609.8879999999999</v>
+        <v>628.947</v>
       </c>
       <c r="G34">
         <v>265.5</v>
@@ -4075,28 +4075,28 @@
         <v>181.4</v>
       </c>
       <c r="M34">
-        <v>33.72680639999999</v>
+        <v>34.7807691</v>
       </c>
       <c r="N34">
-        <v>147.6731936</v>
+        <v>146.6192309</v>
       </c>
       <c r="O34">
-        <v>28.057906784</v>
+        <v>27.857653871</v>
       </c>
       <c r="P34">
-        <v>119.615286816</v>
+        <v>118.761577029</v>
       </c>
       <c r="Q34">
-        <v>144.015286816</v>
+        <v>143.161577029</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08528819665070969</v>
+        <v>0.08579649585878572</v>
       </c>
       <c r="T34">
-        <v>0.7696984520641066</v>
+        <v>0.7796061497263267</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.378511023207938</v>
+        <v>5.215525840686484</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07226534222538643</v>
+        <v>0.07220095072829026</v>
       </c>
       <c r="C35">
-        <v>1322.980961699483</v>
+        <v>1305.355274367784</v>
       </c>
       <c r="D35">
-        <v>1686.427961699483</v>
+        <v>1687.861274367784</v>
       </c>
       <c r="E35">
-        <v>615.847</v>
+        <v>634.9059999999999</v>
       </c>
       <c r="F35">
-        <v>628.947</v>
+        <v>648.006</v>
       </c>
       <c r="G35">
         <v>265.5</v>
@@ -4157,28 +4157,28 @@
         <v>181.4</v>
       </c>
       <c r="M35">
-        <v>34.7807691</v>
+        <v>35.8347318</v>
       </c>
       <c r="N35">
-        <v>146.6192309</v>
+        <v>145.5652682</v>
       </c>
       <c r="O35">
-        <v>27.857653871</v>
+        <v>27.657400958</v>
       </c>
       <c r="P35">
-        <v>118.761577029</v>
+        <v>117.907867242</v>
       </c>
       <c r="Q35">
-        <v>143.161577029</v>
+        <v>142.307867242</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08579649585878572</v>
+        <v>0.08632019807316707</v>
       </c>
       <c r="T35">
-        <v>0.7796061497263267</v>
+        <v>0.7898140806510383</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.215525840686484</v>
+        <v>5.062128021842764</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07220095072829026</v>
+        <v>0.07213655923119411</v>
       </c>
       <c r="C36">
-        <v>1305.355274367784</v>
+        <v>1287.732025483241</v>
       </c>
       <c r="D36">
-        <v>1687.861274367784</v>
+        <v>1689.297025483241</v>
       </c>
       <c r="E36">
-        <v>634.9059999999999</v>
+        <v>653.965</v>
       </c>
       <c r="F36">
-        <v>648.006</v>
+        <v>667.0650000000001</v>
       </c>
       <c r="G36">
         <v>265.5</v>
@@ -4239,28 +4239,28 @@
         <v>181.4</v>
       </c>
       <c r="M36">
-        <v>35.8347318</v>
+        <v>36.88869450000001</v>
       </c>
       <c r="N36">
-        <v>145.5652682</v>
+        <v>144.5113055</v>
       </c>
       <c r="O36">
-        <v>27.657400958</v>
+        <v>27.457148045</v>
       </c>
       <c r="P36">
-        <v>117.907867242</v>
+        <v>117.054157455</v>
       </c>
       <c r="Q36">
-        <v>142.307867242</v>
+        <v>141.454157455</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08632019807316707</v>
+        <v>0.08686001420183709</v>
       </c>
       <c r="T36">
-        <v>0.7898140806510383</v>
+        <v>0.8003361017580486</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.062128021842764</v>
+        <v>4.917495792647256</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07213655923119411</v>
+        <v>0.07207216773409793</v>
       </c>
       <c r="C37">
-        <v>1287.732025483241</v>
+        <v>1270.111221273825</v>
       </c>
       <c r="D37">
-        <v>1689.297025483241</v>
+        <v>1690.735221273825</v>
       </c>
       <c r="E37">
-        <v>653.965</v>
+        <v>673.024</v>
       </c>
       <c r="F37">
-        <v>667.0650000000001</v>
+        <v>686.124</v>
       </c>
       <c r="G37">
         <v>265.5</v>
@@ -4321,28 +4321,28 @@
         <v>181.4</v>
       </c>
       <c r="M37">
-        <v>36.88869450000001</v>
+        <v>37.9426572</v>
       </c>
       <c r="N37">
-        <v>144.5113055</v>
+        <v>143.4573428</v>
       </c>
       <c r="O37">
-        <v>27.457148045</v>
+        <v>27.256895132</v>
       </c>
       <c r="P37">
-        <v>117.054157455</v>
+        <v>116.200447668</v>
       </c>
       <c r="Q37">
-        <v>141.454157455</v>
+        <v>140.600447668</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08686001420183709</v>
+        <v>0.08741669958452802</v>
       </c>
       <c r="T37">
-        <v>0.8003361017580486</v>
+        <v>0.8111869360246532</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.917495792647256</v>
+        <v>4.780898687295943</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07207216773409794</v>
+        <v>0.07200777623700177</v>
       </c>
       <c r="C38">
-        <v>1270.111221273825</v>
+        <v>1252.492867988735</v>
       </c>
       <c r="D38">
-        <v>1690.735221273825</v>
+        <v>1692.175867988735</v>
       </c>
       <c r="E38">
-        <v>673.0239999999999</v>
+        <v>692.083</v>
       </c>
       <c r="F38">
-        <v>686.1239999999999</v>
+        <v>705.183</v>
       </c>
       <c r="G38">
         <v>265.5</v>
@@ -4403,28 +4403,28 @@
         <v>181.4</v>
       </c>
       <c r="M38">
-        <v>37.9426572</v>
+        <v>38.9966199</v>
       </c>
       <c r="N38">
-        <v>143.4573428</v>
+        <v>142.4033801</v>
       </c>
       <c r="O38">
-        <v>27.256895132</v>
+        <v>27.056642219</v>
       </c>
       <c r="P38">
-        <v>116.200447668</v>
+        <v>115.346737881</v>
       </c>
       <c r="Q38">
-        <v>140.600447668</v>
+        <v>139.746737881</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08741669958452802</v>
+        <v>0.08799105751905044</v>
       </c>
       <c r="T38">
-        <v>0.8111869360246531</v>
+        <v>0.8223822412203562</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.780898687295943</v>
+        <v>4.651685209260918</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07200777623700177</v>
+        <v>0.07194338473990561</v>
       </c>
       <c r="C39">
-        <v>1252.492867988735</v>
+        <v>1234.876971898486</v>
       </c>
       <c r="D39">
-        <v>1692.175867988735</v>
+        <v>1693.618971898486</v>
       </c>
       <c r="E39">
-        <v>692.083</v>
+        <v>711.1419999999999</v>
       </c>
       <c r="F39">
-        <v>705.183</v>
+        <v>724.242</v>
       </c>
       <c r="G39">
         <v>265.5</v>
@@ -4485,28 +4485,28 @@
         <v>181.4</v>
       </c>
       <c r="M39">
-        <v>38.9966199</v>
+        <v>40.0505826</v>
       </c>
       <c r="N39">
-        <v>142.4033801</v>
+        <v>141.3494174</v>
       </c>
       <c r="O39">
-        <v>27.056642219</v>
+        <v>26.856389306</v>
       </c>
       <c r="P39">
-        <v>115.346737881</v>
+        <v>114.493028094</v>
       </c>
       <c r="Q39">
-        <v>139.746737881</v>
+        <v>138.893028094</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08799105751905044</v>
+        <v>0.08858394312888002</v>
       </c>
       <c r="T39">
-        <v>0.8223822412203562</v>
+        <v>0.83393868529334</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.651685209260918</v>
+        <v>4.529272440596158</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07194338473990561</v>
+        <v>0.07266874324280945</v>
       </c>
       <c r="C40">
-        <v>1234.876971898486</v>
+        <v>1199.702621375422</v>
       </c>
       <c r="D40">
-        <v>1693.618971898486</v>
+        <v>1677.503621375422</v>
       </c>
       <c r="E40">
-        <v>711.1419999999999</v>
+        <v>730.2009999999999</v>
       </c>
       <c r="F40">
-        <v>724.242</v>
+        <v>743.3009999999999</v>
       </c>
       <c r="G40">
         <v>265.5</v>
@@ -4567,45 +4567,45 @@
         <v>181.4</v>
       </c>
       <c r="M40">
-        <v>40.0505826</v>
+        <v>42.9627978</v>
       </c>
       <c r="N40">
-        <v>141.3494174</v>
+        <v>138.4372022</v>
       </c>
       <c r="O40">
-        <v>26.856389306</v>
+        <v>26.303068418</v>
       </c>
       <c r="P40">
-        <v>114.493028094</v>
+        <v>112.134133782</v>
       </c>
       <c r="Q40">
-        <v>138.893028094</v>
+        <v>136.534133782</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08858394312888002</v>
+        <v>0.08919626761116303</v>
       </c>
       <c r="T40">
-        <v>0.83393868529334</v>
+        <v>0.8458740291719954</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.19</v>
       </c>
       <c r="W40">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.529272440596158</v>
+        <v>4.222257610978957</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07266874324280945</v>
+        <v>0.07262460174571329</v>
       </c>
       <c r="C41">
-        <v>1199.702621375422</v>
+        <v>1181.615547861319</v>
       </c>
       <c r="D41">
-        <v>1677.503621375422</v>
+        <v>1678.475547861319</v>
       </c>
       <c r="E41">
-        <v>730.2009999999999</v>
+        <v>749.26</v>
       </c>
       <c r="F41">
-        <v>743.3009999999999</v>
+        <v>762.36</v>
       </c>
       <c r="G41">
         <v>265.5</v>
@@ -4649,28 +4649,28 @@
         <v>181.4</v>
       </c>
       <c r="M41">
-        <v>42.9627978</v>
+        <v>44.06440800000001</v>
       </c>
       <c r="N41">
-        <v>138.4372022</v>
+        <v>137.335592</v>
       </c>
       <c r="O41">
-        <v>26.303068418</v>
+        <v>26.09376248</v>
       </c>
       <c r="P41">
-        <v>112.134133782</v>
+        <v>111.24182952</v>
       </c>
       <c r="Q41">
-        <v>136.534133782</v>
+        <v>135.64182952</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08919626761116303</v>
+        <v>0.08982900290952214</v>
       </c>
       <c r="T41">
-        <v>0.8458740291719954</v>
+        <v>0.858207217846606</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.222257610978957</v>
+        <v>4.116701170704482</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07262460174571329</v>
+        <v>0.07258046024861711</v>
       </c>
       <c r="C42">
-        <v>1181.615547861319</v>
+        <v>1163.529601246393</v>
       </c>
       <c r="D42">
-        <v>1678.475547861319</v>
+        <v>1679.448601246393</v>
       </c>
       <c r="E42">
-        <v>749.26</v>
+        <v>768.319</v>
       </c>
       <c r="F42">
-        <v>762.36</v>
+        <v>781.419</v>
       </c>
       <c r="G42">
         <v>265.5</v>
@@ -4731,28 +4731,28 @@
         <v>181.4</v>
       </c>
       <c r="M42">
-        <v>44.06440800000001</v>
+        <v>45.1660182</v>
       </c>
       <c r="N42">
-        <v>137.335592</v>
+        <v>136.2339818</v>
       </c>
       <c r="O42">
-        <v>26.09376248</v>
+        <v>25.884456542</v>
       </c>
       <c r="P42">
-        <v>111.24182952</v>
+        <v>110.349525258</v>
       </c>
       <c r="Q42">
-        <v>135.64182952</v>
+        <v>134.749525258</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08982900290952214</v>
+        <v>0.09048318686206291</v>
       </c>
       <c r="T42">
-        <v>0.858207217846606</v>
+        <v>0.8709584807135763</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.116701170704482</v>
+        <v>4.016293825077545</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07258046024861711</v>
+        <v>0.07372701875152096</v>
       </c>
       <c r="C43">
-        <v>1163.529601246393</v>
+        <v>1119.556420183144</v>
       </c>
       <c r="D43">
-        <v>1679.448601246393</v>
+        <v>1654.534420183144</v>
       </c>
       <c r="E43">
-        <v>768.319</v>
+        <v>787.378</v>
       </c>
       <c r="F43">
-        <v>781.419</v>
+        <v>800.4780000000001</v>
       </c>
       <c r="G43">
         <v>265.5</v>
@@ -4813,45 +4813,45 @@
         <v>181.4</v>
       </c>
       <c r="M43">
-        <v>45.1660182</v>
+        <v>49.06930140000001</v>
       </c>
       <c r="N43">
-        <v>136.2339818</v>
+        <v>132.3306986</v>
       </c>
       <c r="O43">
-        <v>25.884456542</v>
+        <v>25.142832734</v>
       </c>
       <c r="P43">
-        <v>110.349525258</v>
+        <v>107.187865866</v>
       </c>
       <c r="Q43">
-        <v>134.749525258</v>
+        <v>131.587865866</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09048318686206291</v>
+        <v>0.09115992888193269</v>
       </c>
       <c r="T43">
-        <v>0.8709584807135763</v>
+        <v>0.8841494423000973</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.19</v>
       </c>
       <c r="W43">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.016293825077545</v>
+        <v>3.696812361791643</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07372701875152096</v>
+        <v>0.0737112272544248</v>
       </c>
       <c r="C44">
-        <v>1119.556420183144</v>
+        <v>1100.83554070804</v>
       </c>
       <c r="D44">
-        <v>1654.534420183144</v>
+        <v>1654.87254070804</v>
       </c>
       <c r="E44">
-        <v>787.3779999999999</v>
+        <v>806.4369999999999</v>
       </c>
       <c r="F44">
-        <v>800.478</v>
+        <v>819.5369999999999</v>
       </c>
       <c r="G44">
         <v>265.5</v>
@@ -4895,28 +4895,28 @@
         <v>181.4</v>
       </c>
       <c r="M44">
-        <v>49.0693014</v>
+        <v>50.2376181</v>
       </c>
       <c r="N44">
-        <v>132.3306986</v>
+        <v>131.1623819</v>
       </c>
       <c r="O44">
-        <v>25.142832734</v>
+        <v>24.920852561</v>
       </c>
       <c r="P44">
-        <v>107.187865866</v>
+        <v>106.241529339</v>
       </c>
       <c r="Q44">
-        <v>131.587865866</v>
+        <v>130.641529339</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09115992888193268</v>
+        <v>0.09186041623583296</v>
       </c>
       <c r="T44">
-        <v>0.8841494423000972</v>
+        <v>0.8978032446440399</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.696812361791644</v>
+        <v>3.610839981284861</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0737112272544248</v>
+        <v>0.07369543575732863</v>
       </c>
       <c r="C45">
-        <v>1100.83554070804</v>
+        <v>1082.114799457751</v>
       </c>
       <c r="D45">
-        <v>1654.87254070804</v>
+        <v>1655.210799457751</v>
       </c>
       <c r="E45">
-        <v>806.4369999999999</v>
+        <v>825.4959999999999</v>
       </c>
       <c r="F45">
-        <v>819.5369999999999</v>
+        <v>838.5959999999999</v>
       </c>
       <c r="G45">
         <v>265.5</v>
@@ -4977,28 +4977,28 @@
         <v>181.4</v>
       </c>
       <c r="M45">
-        <v>50.2376181</v>
+        <v>51.40593479999999</v>
       </c>
       <c r="N45">
-        <v>131.1623819</v>
+        <v>129.9940652</v>
       </c>
       <c r="O45">
-        <v>24.920852561</v>
+        <v>24.69887238800001</v>
       </c>
       <c r="P45">
-        <v>106.241529339</v>
+        <v>105.295192812</v>
       </c>
       <c r="Q45">
-        <v>130.641529339</v>
+        <v>129.695192812</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09186041623583296</v>
+        <v>0.09258592099522969</v>
       </c>
       <c r="T45">
-        <v>0.8978032446440399</v>
+        <v>0.9119446827859807</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.610839981284861</v>
+        <v>3.52877543625566</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07369543575732863</v>
+        <v>0.07470024426023247</v>
       </c>
       <c r="C46">
-        <v>1082.114799457751</v>
+        <v>1041.804486337343</v>
       </c>
       <c r="D46">
-        <v>1655.210799457751</v>
+        <v>1633.959486337343</v>
       </c>
       <c r="E46">
-        <v>825.4959999999999</v>
+        <v>844.5549999999999</v>
       </c>
       <c r="F46">
-        <v>838.5959999999999</v>
+        <v>857.655</v>
       </c>
       <c r="G46">
         <v>265.5</v>
@@ -5059,45 +5059,45 @@
         <v>181.4</v>
       </c>
       <c r="M46">
-        <v>51.40593479999999</v>
+        <v>54.9756855</v>
       </c>
       <c r="N46">
-        <v>129.9940652</v>
+        <v>126.4243145</v>
       </c>
       <c r="O46">
-        <v>24.69887238800001</v>
+        <v>24.020619755</v>
       </c>
       <c r="P46">
-        <v>105.295192812</v>
+        <v>102.403694745</v>
       </c>
       <c r="Q46">
-        <v>129.695192812</v>
+        <v>126.803694745</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09258592099522969</v>
+        <v>0.0933378077458772</v>
       </c>
       <c r="T46">
-        <v>0.9119446827859807</v>
+        <v>0.9266003550421736</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.19</v>
       </c>
       <c r="W46">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.52877543625566</v>
+        <v>3.299640529266342</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07470024426023247</v>
+        <v>0.07470713276313631</v>
       </c>
       <c r="C47">
-        <v>1041.804486337343</v>
+        <v>1022.601680318542</v>
       </c>
       <c r="D47">
-        <v>1633.959486337343</v>
+        <v>1633.815680318542</v>
       </c>
       <c r="E47">
-        <v>844.5549999999999</v>
+        <v>863.6139999999999</v>
       </c>
       <c r="F47">
-        <v>857.655</v>
+        <v>876.7139999999999</v>
       </c>
       <c r="G47">
         <v>265.5</v>
@@ -5141,28 +5141,28 @@
         <v>181.4</v>
       </c>
       <c r="M47">
-        <v>54.9756855</v>
+        <v>56.1973674</v>
       </c>
       <c r="N47">
-        <v>126.4243145</v>
+        <v>125.2026326</v>
       </c>
       <c r="O47">
-        <v>24.020619755</v>
+        <v>23.788500194</v>
       </c>
       <c r="P47">
-        <v>102.403694745</v>
+        <v>101.414132406</v>
       </c>
       <c r="Q47">
-        <v>126.803694745</v>
+        <v>125.814132406</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.0933378077458772</v>
+        <v>0.09411754215395612</v>
       </c>
       <c r="T47">
-        <v>0.9266003550421736</v>
+        <v>0.9417988299745221</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.299640529266342</v>
+        <v>3.227909213412727</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07470713276313631</v>
+        <v>0.07471402126604015</v>
       </c>
       <c r="C48">
-        <v>1022.601680318542</v>
+        <v>1003.398899610468</v>
       </c>
       <c r="D48">
-        <v>1633.815680318542</v>
+        <v>1633.671899610468</v>
       </c>
       <c r="E48">
-        <v>863.6139999999999</v>
+        <v>882.673</v>
       </c>
       <c r="F48">
-        <v>876.7139999999999</v>
+        <v>895.773</v>
       </c>
       <c r="G48">
         <v>265.5</v>
@@ -5223,28 +5223,28 @@
         <v>181.4</v>
       </c>
       <c r="M48">
-        <v>56.1973674</v>
+        <v>57.4190493</v>
       </c>
       <c r="N48">
-        <v>125.2026326</v>
+        <v>123.9809507</v>
       </c>
       <c r="O48">
-        <v>23.788500194</v>
+        <v>23.556380633</v>
       </c>
       <c r="P48">
-        <v>101.414132406</v>
+        <v>100.424570067</v>
       </c>
       <c r="Q48">
-        <v>125.814132406</v>
+        <v>124.824570067</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09411754215395612</v>
+        <v>0.09492670050196253</v>
       </c>
       <c r="T48">
-        <v>0.9417988299745221</v>
+        <v>0.9575708322628083</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.227909213412727</v>
+        <v>3.159230293978413</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07471402126604015</v>
+        <v>0.07472090976894399</v>
       </c>
       <c r="C49">
-        <v>1003.398899610468</v>
+        <v>984.1961442064386</v>
       </c>
       <c r="D49">
-        <v>1633.671899610468</v>
+        <v>1633.528144206439</v>
       </c>
       <c r="E49">
-        <v>882.673</v>
+        <v>901.732</v>
       </c>
       <c r="F49">
-        <v>895.773</v>
+        <v>914.832</v>
       </c>
       <c r="G49">
         <v>265.5</v>
@@ -5305,28 +5305,28 @@
         <v>181.4</v>
       </c>
       <c r="M49">
-        <v>57.4190493</v>
+        <v>58.6407312</v>
       </c>
       <c r="N49">
-        <v>123.9809507</v>
+        <v>122.7592688</v>
       </c>
       <c r="O49">
-        <v>23.556380633</v>
+        <v>23.324261072</v>
       </c>
       <c r="P49">
-        <v>100.424570067</v>
+        <v>99.435007728</v>
       </c>
       <c r="Q49">
-        <v>124.824570067</v>
+        <v>123.835007728</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09492670050196253</v>
+        <v>0.09576698032489227</v>
       </c>
       <c r="T49">
-        <v>0.9575708322628083</v>
+        <v>0.9739494500237208</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.159230293978413</v>
+        <v>3.093412996187196</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07472090976894398</v>
+        <v>0.07472779827184782</v>
       </c>
       <c r="C50">
-        <v>984.1961442064389</v>
+        <v>964.9934140997756</v>
       </c>
       <c r="D50">
-        <v>1633.528144206439</v>
+        <v>1633.384414099776</v>
       </c>
       <c r="E50">
-        <v>901.7319999999999</v>
+        <v>920.7909999999999</v>
       </c>
       <c r="F50">
-        <v>914.8319999999999</v>
+        <v>933.891</v>
       </c>
       <c r="G50">
         <v>265.5</v>
@@ -5387,28 +5387,28 @@
         <v>181.4</v>
       </c>
       <c r="M50">
-        <v>58.6407312</v>
+        <v>59.8624131</v>
       </c>
       <c r="N50">
-        <v>122.7592688</v>
+        <v>121.5375869</v>
       </c>
       <c r="O50">
-        <v>23.324261072</v>
+        <v>23.092141511</v>
       </c>
       <c r="P50">
-        <v>99.435007728</v>
+        <v>98.44544538900001</v>
       </c>
       <c r="Q50">
-        <v>123.835007728</v>
+        <v>122.845445389</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09576698032489225</v>
+        <v>0.09664021229774081</v>
       </c>
       <c r="T50">
-        <v>0.9739494500237206</v>
+        <v>0.9909703665203552</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.093412996187197</v>
+        <v>3.030282118713988</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07472779827184782</v>
+        <v>0.07789368677475166</v>
       </c>
       <c r="C51">
-        <v>964.9934140997756</v>
+        <v>882.4504538014386</v>
       </c>
       <c r="D51">
-        <v>1633.384414099776</v>
+        <v>1569.900453801439</v>
       </c>
       <c r="E51">
-        <v>920.7909999999999</v>
+        <v>939.8499999999999</v>
       </c>
       <c r="F51">
-        <v>933.891</v>
+        <v>952.9499999999999</v>
       </c>
       <c r="G51">
         <v>265.5</v>
@@ -5469,45 +5469,45 @@
         <v>181.4</v>
       </c>
       <c r="M51">
-        <v>59.8624131</v>
+        <v>68.517105</v>
       </c>
       <c r="N51">
-        <v>121.5375869</v>
+        <v>112.882895</v>
       </c>
       <c r="O51">
-        <v>23.092141511</v>
+        <v>21.44775005</v>
       </c>
       <c r="P51">
-        <v>98.44544538900001</v>
+        <v>91.43514495000001</v>
       </c>
       <c r="Q51">
-        <v>122.845445389</v>
+        <v>115.83514495</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09664021229774081</v>
+        <v>0.0975483735495033</v>
       </c>
       <c r="T51">
-        <v>0.9909703665203552</v>
+        <v>1.008672119676855</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.19</v>
       </c>
       <c r="W51">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.030282118713988</v>
+        <v>2.647514076959323</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07789368677475166</v>
+        <v>0.07796375527765549</v>
       </c>
       <c r="C52">
-        <v>882.4504538014386</v>
+        <v>862.0421755523461</v>
       </c>
       <c r="D52">
-        <v>1569.900453801439</v>
+        <v>1568.551175552346</v>
       </c>
       <c r="E52">
-        <v>939.8499999999999</v>
+        <v>958.9089999999999</v>
       </c>
       <c r="F52">
-        <v>952.9499999999999</v>
+        <v>972.0089999999999</v>
       </c>
       <c r="G52">
         <v>265.5</v>
@@ -5551,28 +5551,28 @@
         <v>181.4</v>
       </c>
       <c r="M52">
-        <v>68.517105</v>
+        <v>69.8874471</v>
       </c>
       <c r="N52">
-        <v>112.882895</v>
+        <v>111.5125529</v>
       </c>
       <c r="O52">
-        <v>21.44775005</v>
+        <v>21.187385051</v>
       </c>
       <c r="P52">
-        <v>91.43514495000001</v>
+        <v>90.325167849</v>
       </c>
       <c r="Q52">
-        <v>115.83514495</v>
+        <v>114.725167849</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.0975483735495033</v>
+        <v>0.09849360260746018</v>
       </c>
       <c r="T52">
-        <v>1.008672119676855</v>
+        <v>1.027096393370355</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.647514076959323</v>
+        <v>2.59560203623463</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07796375527765549</v>
+        <v>0.07803382378055933</v>
       </c>
       <c r="C53">
-        <v>862.0421755523461</v>
+        <v>841.6362146329004</v>
       </c>
       <c r="D53">
-        <v>1568.551175552346</v>
+        <v>1567.2042146329</v>
       </c>
       <c r="E53">
-        <v>958.9089999999999</v>
+        <v>977.968</v>
       </c>
       <c r="F53">
-        <v>972.0089999999999</v>
+        <v>991.068</v>
       </c>
       <c r="G53">
         <v>265.5</v>
@@ -5633,28 +5633,28 @@
         <v>181.4</v>
       </c>
       <c r="M53">
-        <v>69.8874471</v>
+        <v>71.2577892</v>
       </c>
       <c r="N53">
-        <v>111.5125529</v>
+        <v>110.1422108</v>
       </c>
       <c r="O53">
-        <v>21.187385051</v>
+        <v>20.927020052</v>
       </c>
       <c r="P53">
-        <v>90.325167849</v>
+        <v>89.215190748</v>
       </c>
       <c r="Q53">
-        <v>114.725167849</v>
+        <v>113.615190748</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09849360260746018</v>
+        <v>0.09947821620949859</v>
       </c>
       <c r="T53">
-        <v>1.027096393370355</v>
+        <v>1.046288345134417</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.59560203623463</v>
+        <v>2.545686612460887</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07803382378055933</v>
+        <v>0.07977816228346316</v>
       </c>
       <c r="C54">
-        <v>841.6362146329004</v>
+        <v>789.7749836249134</v>
       </c>
       <c r="D54">
-        <v>1567.2042146329</v>
+        <v>1534.401983624913</v>
       </c>
       <c r="E54">
-        <v>977.968</v>
+        <v>997.0269999999999</v>
       </c>
       <c r="F54">
-        <v>991.068</v>
+        <v>1010.127</v>
       </c>
       <c r="G54">
         <v>265.5</v>
@@ -5715,45 +5715,45 @@
         <v>181.4</v>
       </c>
       <c r="M54">
-        <v>71.2577892</v>
+        <v>76.5676266</v>
       </c>
       <c r="N54">
-        <v>110.1422108</v>
+        <v>104.8323734</v>
       </c>
       <c r="O54">
-        <v>20.927020052</v>
+        <v>19.918150946</v>
       </c>
       <c r="P54">
-        <v>89.215190748</v>
+        <v>84.91422245400001</v>
       </c>
       <c r="Q54">
-        <v>113.615190748</v>
+        <v>109.314222454</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09947821620949859</v>
+        <v>0.1005047282626876</v>
       </c>
       <c r="T54">
-        <v>1.046288345134417</v>
+        <v>1.066296975696951</v>
       </c>
       <c r="U54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.19</v>
       </c>
       <c r="W54">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.545686612460887</v>
+        <v>2.369147485106976</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07977816228346316</v>
+        <v>0.07987982078636699</v>
       </c>
       <c r="C55">
-        <v>789.7749836249134</v>
+        <v>768.8465913074601</v>
       </c>
       <c r="D55">
-        <v>1534.401983624913</v>
+        <v>1532.53259130746</v>
       </c>
       <c r="E55">
-        <v>997.0269999999999</v>
+        <v>1016.086</v>
       </c>
       <c r="F55">
-        <v>1010.127</v>
+        <v>1029.186</v>
       </c>
       <c r="G55">
         <v>265.5</v>
@@ -5797,28 +5797,28 @@
         <v>181.4</v>
       </c>
       <c r="M55">
-        <v>76.5676266</v>
+        <v>78.0122988</v>
       </c>
       <c r="N55">
-        <v>104.8323734</v>
+        <v>103.3877012</v>
       </c>
       <c r="O55">
-        <v>19.918150946</v>
+        <v>19.643663228</v>
       </c>
       <c r="P55">
-        <v>84.91422245400001</v>
+        <v>83.744037972</v>
       </c>
       <c r="Q55">
-        <v>109.314222454</v>
+        <v>108.144037972</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1005047282626876</v>
+        <v>0.1015758712747108</v>
       </c>
       <c r="T55">
-        <v>1.066296975696951</v>
+        <v>1.087175546718724</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.369147485106976</v>
+        <v>2.325274383530921</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07987982078636699</v>
+        <v>0.07998147928927082</v>
       </c>
       <c r="C56">
-        <v>768.8465913074601</v>
+        <v>747.9227484826176</v>
       </c>
       <c r="D56">
-        <v>1532.53259130746</v>
+        <v>1530.667748482618</v>
       </c>
       <c r="E56">
-        <v>1016.086</v>
+        <v>1035.145</v>
       </c>
       <c r="F56">
-        <v>1029.186</v>
+        <v>1048.245</v>
       </c>
       <c r="G56">
         <v>265.5</v>
@@ -5879,28 +5879,28 @@
         <v>181.4</v>
       </c>
       <c r="M56">
-        <v>78.0122988</v>
+        <v>79.45697100000001</v>
       </c>
       <c r="N56">
-        <v>103.3877012</v>
+        <v>101.943029</v>
       </c>
       <c r="O56">
-        <v>19.643663228</v>
+        <v>19.36917551</v>
       </c>
       <c r="P56">
-        <v>83.744037972</v>
+        <v>82.57385349</v>
       </c>
       <c r="Q56">
-        <v>108.144037972</v>
+        <v>106.97385349</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1015758712747108</v>
+        <v>0.1026946206428241</v>
       </c>
       <c r="T56">
-        <v>1.087175546718724</v>
+        <v>1.108982054230355</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.325274383530921</v>
+        <v>2.282996667466722</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07998147928927082</v>
+        <v>0.08008313779217467</v>
       </c>
       <c r="C57">
-        <v>747.9227484826176</v>
+        <v>727.0034385625936</v>
       </c>
       <c r="D57">
-        <v>1530.667748482618</v>
+        <v>1528.807438562594</v>
       </c>
       <c r="E57">
-        <v>1035.145</v>
+        <v>1054.204</v>
       </c>
       <c r="F57">
-        <v>1048.245</v>
+        <v>1067.304</v>
       </c>
       <c r="G57">
         <v>265.5</v>
@@ -5961,28 +5961,28 @@
         <v>181.4</v>
       </c>
       <c r="M57">
-        <v>79.45697100000001</v>
+        <v>80.90164320000001</v>
       </c>
       <c r="N57">
-        <v>101.943029</v>
+        <v>100.4983568</v>
       </c>
       <c r="O57">
-        <v>19.36917551</v>
+        <v>19.094687792</v>
       </c>
       <c r="P57">
-        <v>82.57385349</v>
+        <v>81.40366900799999</v>
       </c>
       <c r="Q57">
-        <v>106.97385349</v>
+        <v>105.803669008</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1026946206428241</v>
+        <v>0.1038642222549424</v>
       </c>
       <c r="T57">
-        <v>1.108982054230355</v>
+        <v>1.131779766628877</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.282996667466722</v>
+        <v>2.242228869833388</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08008313779217467</v>
+        <v>0.08018479629507852</v>
       </c>
       <c r="C58">
-        <v>727.0034385625936</v>
+        <v>706.0886450401383</v>
       </c>
       <c r="D58">
-        <v>1528.807438562594</v>
+        <v>1526.951645040138</v>
       </c>
       <c r="E58">
-        <v>1054.204</v>
+        <v>1073.263</v>
       </c>
       <c r="F58">
-        <v>1067.304</v>
+        <v>1086.363</v>
       </c>
       <c r="G58">
         <v>265.5</v>
@@ -6043,28 +6043,28 @@
         <v>181.4</v>
       </c>
       <c r="M58">
-        <v>80.90164320000001</v>
+        <v>82.34631540000001</v>
       </c>
       <c r="N58">
-        <v>100.4983568</v>
+        <v>99.0536846</v>
       </c>
       <c r="O58">
-        <v>19.094687792</v>
+        <v>18.820200074</v>
       </c>
       <c r="P58">
-        <v>81.40366900799999</v>
+        <v>80.233484526</v>
       </c>
       <c r="Q58">
-        <v>105.803669008</v>
+        <v>104.633484526</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1038642222549424</v>
+        <v>0.105088223942043</v>
       </c>
       <c r="T58">
-        <v>1.131779766628877</v>
+        <v>1.15563783774361</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.242228869833388</v>
+        <v>2.202891521239819</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08018479629507852</v>
+        <v>0.08028645479798235</v>
       </c>
       <c r="C59">
-        <v>706.0886450401383</v>
+        <v>685.1783514880567</v>
       </c>
       <c r="D59">
-        <v>1526.951645040138</v>
+        <v>1525.100351488057</v>
       </c>
       <c r="E59">
-        <v>1073.263</v>
+        <v>1092.322</v>
       </c>
       <c r="F59">
-        <v>1086.363</v>
+        <v>1105.422</v>
       </c>
       <c r="G59">
         <v>265.5</v>
@@ -6125,28 +6125,28 @@
         <v>181.4</v>
       </c>
       <c r="M59">
-        <v>82.34631540000001</v>
+        <v>83.79098760000001</v>
       </c>
       <c r="N59">
-        <v>99.0536846</v>
+        <v>97.6090124</v>
       </c>
       <c r="O59">
-        <v>18.820200074</v>
+        <v>18.545712356</v>
       </c>
       <c r="P59">
-        <v>80.233484526</v>
+        <v>79.063300044</v>
       </c>
       <c r="Q59">
-        <v>104.633484526</v>
+        <v>103.463300044</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.105088223942043</v>
+        <v>0.1063705114237675</v>
       </c>
       <c r="T59">
-        <v>1.15563783774361</v>
+        <v>1.180632007482854</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.202891521239819</v>
+        <v>2.164910632942581</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08028645479798235</v>
+        <v>0.08038811330088619</v>
       </c>
       <c r="C60">
-        <v>685.1783514880569</v>
+        <v>664.2725415587227</v>
       </c>
       <c r="D60">
-        <v>1525.100351488057</v>
+        <v>1523.253541558722</v>
       </c>
       <c r="E60">
-        <v>1092.322</v>
+        <v>1111.381</v>
       </c>
       <c r="F60">
-        <v>1105.422</v>
+        <v>1124.481</v>
       </c>
       <c r="G60">
         <v>265.5</v>
@@ -6207,28 +6207,28 @@
         <v>181.4</v>
       </c>
       <c r="M60">
-        <v>83.79098759999999</v>
+        <v>85.23565979999999</v>
       </c>
       <c r="N60">
-        <v>97.60901240000001</v>
+        <v>96.16434020000001</v>
       </c>
       <c r="O60">
-        <v>18.545712356</v>
+        <v>18.271224638</v>
       </c>
       <c r="P60">
-        <v>79.06330004400002</v>
+        <v>77.89311556200001</v>
       </c>
       <c r="Q60">
-        <v>103.463300044</v>
+        <v>102.293115562</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1063705114237675</v>
+        <v>0.1077153495143565</v>
       </c>
       <c r="T60">
-        <v>1.180632007482854</v>
+        <v>1.206845405014256</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.164910632942582</v>
+        <v>2.128217232384233</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08038811330088619</v>
+        <v>0.08048977180379002</v>
       </c>
       <c r="C61">
-        <v>664.2725415587227</v>
+        <v>643.3711989835986</v>
       </c>
       <c r="D61">
-        <v>1523.253541558722</v>
+        <v>1521.411198983599</v>
       </c>
       <c r="E61">
-        <v>1111.381</v>
+        <v>1130.44</v>
       </c>
       <c r="F61">
-        <v>1124.481</v>
+        <v>1143.54</v>
       </c>
       <c r="G61">
         <v>265.5</v>
@@ -6289,28 +6289,28 @@
         <v>181.4</v>
       </c>
       <c r="M61">
-        <v>85.23565979999999</v>
+        <v>86.68033200000001</v>
       </c>
       <c r="N61">
-        <v>96.16434020000001</v>
+        <v>94.719668</v>
       </c>
       <c r="O61">
-        <v>18.271224638</v>
+        <v>17.99673692</v>
       </c>
       <c r="P61">
-        <v>77.89311556200001</v>
+        <v>76.72293108</v>
       </c>
       <c r="Q61">
-        <v>102.293115562</v>
+        <v>101.12293108</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1077153495143565</v>
+        <v>0.109127429509475</v>
       </c>
       <c r="T61">
-        <v>1.206845405014256</v>
+        <v>1.234369472422229</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.128217232384233</v>
+        <v>2.092746945177828</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08048977180379002</v>
+        <v>0.08059143030669386</v>
       </c>
       <c r="C62">
-        <v>643.3711989835986</v>
+        <v>622.4743075727577</v>
       </c>
       <c r="D62">
-        <v>1521.411198983599</v>
+        <v>1519.573307572758</v>
       </c>
       <c r="E62">
-        <v>1130.44</v>
+        <v>1149.499</v>
       </c>
       <c r="F62">
-        <v>1143.54</v>
+        <v>1162.599</v>
       </c>
       <c r="G62">
         <v>265.5</v>
@@ -6371,28 +6371,28 @@
         <v>181.4</v>
       </c>
       <c r="M62">
-        <v>86.68033200000001</v>
+        <v>88.12500420000001</v>
       </c>
       <c r="N62">
-        <v>94.719668</v>
+        <v>93.2749958</v>
       </c>
       <c r="O62">
-        <v>17.99673692</v>
+        <v>17.722249202</v>
       </c>
       <c r="P62">
-        <v>76.72293108</v>
+        <v>75.552746598</v>
       </c>
       <c r="Q62">
-        <v>101.12293108</v>
+        <v>99.952746598</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.109127429509475</v>
+        <v>0.1106119238633176</v>
       </c>
       <c r="T62">
-        <v>1.234369472422229</v>
+        <v>1.263305030466507</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.092746945177828</v>
+        <v>2.0584396182077</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08059143030669386</v>
+        <v>0.08069308880959769</v>
       </c>
       <c r="C63">
-        <v>622.4743075727577</v>
+        <v>601.5818512144103</v>
       </c>
       <c r="D63">
-        <v>1519.573307572758</v>
+        <v>1517.73985121441</v>
       </c>
       <c r="E63">
-        <v>1149.499</v>
+        <v>1168.558</v>
       </c>
       <c r="F63">
-        <v>1162.599</v>
+        <v>1181.658</v>
       </c>
       <c r="G63">
         <v>265.5</v>
@@ -6453,28 +6453,28 @@
         <v>181.4</v>
       </c>
       <c r="M63">
-        <v>88.12500420000001</v>
+        <v>89.56967640000001</v>
       </c>
       <c r="N63">
-        <v>93.2749958</v>
+        <v>91.8303236</v>
       </c>
       <c r="O63">
-        <v>17.722249202</v>
+        <v>17.447761484</v>
       </c>
       <c r="P63">
-        <v>75.552746598</v>
+        <v>74.382562116</v>
       </c>
       <c r="Q63">
-        <v>99.952746598</v>
+        <v>98.78256211600001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1106119238633176</v>
+        <v>0.1121745494989413</v>
       </c>
       <c r="T63">
-        <v>1.263305030466507</v>
+        <v>1.29376351261838</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.0584396182077</v>
+        <v>2.02523897920435</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08069308880959769</v>
+        <v>0.08804100731250152</v>
       </c>
       <c r="C64">
-        <v>601.5818512144103</v>
+        <v>460.7772776928368</v>
       </c>
       <c r="D64">
-        <v>1517.73985121441</v>
+        <v>1395.994277692837</v>
       </c>
       <c r="E64">
-        <v>1168.558</v>
+        <v>1187.617</v>
       </c>
       <c r="F64">
-        <v>1181.658</v>
+        <v>1200.717</v>
       </c>
       <c r="G64">
         <v>265.5</v>
@@ -6535,45 +6535,45 @@
         <v>181.4</v>
       </c>
       <c r="M64">
-        <v>89.56967640000001</v>
+        <v>108.06453</v>
       </c>
       <c r="N64">
-        <v>91.8303236</v>
+        <v>73.33547000000002</v>
       </c>
       <c r="O64">
-        <v>17.447761484</v>
+        <v>13.9337393</v>
       </c>
       <c r="P64">
-        <v>74.382562116</v>
+        <v>59.40173070000002</v>
       </c>
       <c r="Q64">
-        <v>98.78256211600001</v>
+        <v>83.80173070000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1121745494989413</v>
+        <v>0.1138216413851392</v>
       </c>
       <c r="T64">
-        <v>1.29376351261838</v>
+        <v>1.325868399210894</v>
       </c>
       <c r="U64">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V64">
         <v>0.19</v>
       </c>
       <c r="W64">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.02523897920435</v>
+        <v>1.678626650206132</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08804100731250152</v>
+        <v>0.08825768581540536</v>
       </c>
       <c r="C65">
-        <v>460.7772776928368</v>
+        <v>438.4239643725682</v>
       </c>
       <c r="D65">
-        <v>1395.994277692837</v>
+        <v>1392.699964372568</v>
       </c>
       <c r="E65">
-        <v>1187.617</v>
+        <v>1206.676</v>
       </c>
       <c r="F65">
-        <v>1200.717</v>
+        <v>1219.776</v>
       </c>
       <c r="G65">
         <v>265.5</v>
@@ -6617,28 +6617,28 @@
         <v>181.4</v>
       </c>
       <c r="M65">
-        <v>108.06453</v>
+        <v>109.77984</v>
       </c>
       <c r="N65">
-        <v>73.33547000000002</v>
+        <v>71.62016000000003</v>
       </c>
       <c r="O65">
-        <v>13.9337393</v>
+        <v>13.6078304</v>
       </c>
       <c r="P65">
-        <v>59.40173070000002</v>
+        <v>58.01232960000002</v>
       </c>
       <c r="Q65">
-        <v>83.80173070000002</v>
+        <v>82.41232960000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1138216413851392</v>
+        <v>0.115560238376126</v>
       </c>
       <c r="T65">
-        <v>1.325868399210894</v>
+        <v>1.359756890614103</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.678626650206132</v>
+        <v>1.652398108796661</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08825768581540536</v>
+        <v>0.08847436431830918</v>
       </c>
       <c r="C66">
-        <v>438.4239643725682</v>
+        <v>416.0861625062221</v>
       </c>
       <c r="D66">
-        <v>1392.699964372568</v>
+        <v>1389.421162506222</v>
       </c>
       <c r="E66">
-        <v>1206.676</v>
+        <v>1225.735</v>
       </c>
       <c r="F66">
-        <v>1219.776</v>
+        <v>1238.835</v>
       </c>
       <c r="G66">
         <v>265.5</v>
@@ -6699,28 +6699,28 @@
         <v>181.4</v>
       </c>
       <c r="M66">
-        <v>109.77984</v>
+        <v>111.49515</v>
       </c>
       <c r="N66">
-        <v>71.62016000000003</v>
+        <v>69.90485000000001</v>
       </c>
       <c r="O66">
-        <v>13.6078304</v>
+        <v>13.2819215</v>
       </c>
       <c r="P66">
-        <v>58.01232960000002</v>
+        <v>56.62292850000001</v>
       </c>
       <c r="Q66">
-        <v>82.41232960000002</v>
+        <v>81.02292850000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.115560238376126</v>
+        <v>0.1173981837665977</v>
       </c>
       <c r="T66">
-        <v>1.359756890614103</v>
+        <v>1.395581867240353</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.652398108796661</v>
+        <v>1.626976599430558</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08847436431830918</v>
+        <v>0.08869104282121304</v>
       </c>
       <c r="C67">
-        <v>416.0861625062221</v>
+        <v>393.7637627963252</v>
       </c>
       <c r="D67">
-        <v>1389.421162506222</v>
+        <v>1386.157762796325</v>
       </c>
       <c r="E67">
-        <v>1225.735</v>
+        <v>1244.794</v>
       </c>
       <c r="F67">
-        <v>1238.835</v>
+        <v>1257.894</v>
       </c>
       <c r="G67">
         <v>265.5</v>
@@ -6781,28 +6781,28 @@
         <v>181.4</v>
       </c>
       <c r="M67">
-        <v>111.49515</v>
+        <v>113.21046</v>
       </c>
       <c r="N67">
-        <v>69.90485000000001</v>
+        <v>68.18954000000001</v>
       </c>
       <c r="O67">
-        <v>13.2819215</v>
+        <v>12.9560126</v>
       </c>
       <c r="P67">
-        <v>56.62292850000001</v>
+        <v>55.23352740000001</v>
       </c>
       <c r="Q67">
-        <v>81.02292850000001</v>
+        <v>79.63352740000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1173981837665977</v>
+        <v>0.119344243591803</v>
       </c>
       <c r="T67">
-        <v>1.395581867240353</v>
+        <v>1.433514195432853</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.626976599430558</v>
+        <v>1.602325438833126</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08869104282121304</v>
+        <v>0.08890772132411687</v>
       </c>
       <c r="C68">
-        <v>393.7637627963252</v>
+        <v>371.456656969847</v>
       </c>
       <c r="D68">
-        <v>1386.157762796325</v>
+        <v>1382.909656969847</v>
       </c>
       <c r="E68">
-        <v>1244.794</v>
+        <v>1263.853</v>
       </c>
       <c r="F68">
-        <v>1257.894</v>
+        <v>1276.953</v>
       </c>
       <c r="G68">
         <v>265.5</v>
@@ -6863,28 +6863,28 @@
         <v>181.4</v>
       </c>
       <c r="M68">
-        <v>113.21046</v>
+        <v>114.92577</v>
       </c>
       <c r="N68">
-        <v>68.18954000000001</v>
+        <v>66.47423000000001</v>
       </c>
       <c r="O68">
-        <v>12.9560126</v>
+        <v>12.6301037</v>
       </c>
       <c r="P68">
-        <v>55.23352740000001</v>
+        <v>53.84412630000001</v>
       </c>
       <c r="Q68">
-        <v>79.63352740000002</v>
+        <v>78.2441263</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.119344243591803</v>
+        <v>0.1214082464367178</v>
       </c>
       <c r="T68">
-        <v>1.433514195432853</v>
+        <v>1.473745452606716</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.602325438833126</v>
+        <v>1.578410133775915</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08890772132411687</v>
+        <v>0.08912439982702069</v>
       </c>
       <c r="C69">
-        <v>371.456656969847</v>
+        <v>349.1647377662243</v>
       </c>
       <c r="D69">
-        <v>1382.909656969847</v>
+        <v>1379.676737766224</v>
       </c>
       <c r="E69">
-        <v>1263.853</v>
+        <v>1282.912</v>
       </c>
       <c r="F69">
-        <v>1276.953</v>
+        <v>1296.012</v>
       </c>
       <c r="G69">
         <v>265.5</v>
@@ -6945,28 +6945,28 @@
         <v>181.4</v>
       </c>
       <c r="M69">
-        <v>114.92577</v>
+        <v>116.64108</v>
       </c>
       <c r="N69">
-        <v>66.47423000000001</v>
+        <v>64.75892000000002</v>
       </c>
       <c r="O69">
-        <v>12.6301037</v>
+        <v>12.3041948</v>
       </c>
       <c r="P69">
-        <v>53.84412630000001</v>
+        <v>52.45472520000001</v>
       </c>
       <c r="Q69">
-        <v>78.2441263</v>
+        <v>76.85472520000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1214082464367178</v>
+        <v>0.1236012494594397</v>
       </c>
       <c r="T69">
-        <v>1.473745452606716</v>
+        <v>1.516491163353946</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.578410133775915</v>
+        <v>1.555198220043916</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08912439982702069</v>
+        <v>0.08934107832992455</v>
       </c>
       <c r="C70">
-        <v>349.1647377662243</v>
+        <v>326.887898925555</v>
       </c>
       <c r="D70">
-        <v>1379.676737766224</v>
+        <v>1376.458898925555</v>
       </c>
       <c r="E70">
-        <v>1282.912</v>
+        <v>1301.971</v>
       </c>
       <c r="F70">
-        <v>1296.012</v>
+        <v>1315.071</v>
       </c>
       <c r="G70">
         <v>265.5</v>
@@ -7027,28 +7027,28 @@
         <v>181.4</v>
       </c>
       <c r="M70">
-        <v>116.64108</v>
+        <v>118.35639</v>
       </c>
       <c r="N70">
-        <v>64.75892000000002</v>
+        <v>63.04361000000002</v>
       </c>
       <c r="O70">
-        <v>12.3041948</v>
+        <v>11.9782859</v>
       </c>
       <c r="P70">
-        <v>52.45472520000001</v>
+        <v>51.06532410000001</v>
       </c>
       <c r="Q70">
-        <v>76.85472520000002</v>
+        <v>75.46532410000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1236012494594397</v>
+        <v>0.1259357365481437</v>
       </c>
       <c r="T70">
-        <v>1.516491163353946</v>
+        <v>1.56199466189132</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.555198220043916</v>
+        <v>1.532659115405599</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08934107832992455</v>
+        <v>0.08955775683282838</v>
       </c>
       <c r="C71">
-        <v>326.887898925555</v>
+        <v>304.626035176957</v>
       </c>
       <c r="D71">
-        <v>1376.458898925555</v>
+        <v>1373.256035176957</v>
       </c>
       <c r="E71">
-        <v>1301.971</v>
+        <v>1321.03</v>
       </c>
       <c r="F71">
-        <v>1315.071</v>
+        <v>1334.13</v>
       </c>
       <c r="G71">
         <v>265.5</v>
@@ -7109,28 +7109,28 @@
         <v>181.4</v>
       </c>
       <c r="M71">
-        <v>118.35639</v>
+        <v>120.0717</v>
       </c>
       <c r="N71">
-        <v>63.04361000000002</v>
+        <v>61.3283</v>
       </c>
       <c r="O71">
-        <v>11.9782859</v>
+        <v>11.652377</v>
       </c>
       <c r="P71">
-        <v>51.06532410000001</v>
+        <v>49.675923</v>
       </c>
       <c r="Q71">
-        <v>75.46532410000002</v>
+        <v>74.075923</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1259357365481437</v>
+        <v>0.1284258561094279</v>
       </c>
       <c r="T71">
-        <v>1.56199466189132</v>
+        <v>1.610531726997852</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.532659115405599</v>
+        <v>1.510763985185518</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08955775683282838</v>
+        <v>0.1244944694718774</v>
       </c>
       <c r="C72">
-        <v>304.626035176957</v>
+        <v>-89.0891608551899</v>
       </c>
       <c r="D72">
-        <v>1373.256035176957</v>
+        <v>998.5998391448101</v>
       </c>
       <c r="E72">
-        <v>1321.03</v>
+        <v>1340.089</v>
       </c>
       <c r="F72">
-        <v>1334.13</v>
+        <v>1353.189</v>
       </c>
       <c r="G72">
         <v>265.5</v>
@@ -7191,45 +7191,45 @@
         <v>181.4</v>
       </c>
       <c r="M72">
-        <v>120.0717</v>
+        <v>198.6481452</v>
       </c>
       <c r="N72">
-        <v>61.3283</v>
+        <v>-17.24814520000001</v>
       </c>
       <c r="O72">
-        <v>11.652377</v>
+        <v>-3.277147588000002</v>
       </c>
       <c r="P72">
-        <v>49.675923</v>
+        <v>-13.97099761200001</v>
       </c>
       <c r="Q72">
-        <v>74.075923</v>
+        <v>10.429002388</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1284258561094279</v>
+        <v>0.1322424633605104</v>
       </c>
       <c r="T72">
-        <v>1.610531726997852</v>
+        <v>1.68492450616879</v>
       </c>
       <c r="U72">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.19</v>
+        <v>0.173502752644881</v>
       </c>
       <c r="W72">
-        <v>0.07290000000000001</v>
+        <v>0.1213297959117315</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.510763985185518</v>
+        <v>0.9131723823414788</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1244944694718773</v>
+        <v>0.1255044694718774</v>
       </c>
       <c r="C73">
-        <v>-89.08916085518922</v>
+        <v>-115.9626450578828</v>
       </c>
       <c r="D73">
-        <v>998.5998391448105</v>
+        <v>990.7853549421171</v>
       </c>
       <c r="E73">
-        <v>1340.089</v>
+        <v>1359.148</v>
       </c>
       <c r="F73">
-        <v>1353.189</v>
+        <v>1372.248</v>
       </c>
       <c r="G73">
         <v>265.5</v>
@@ -7273,37 +7273,37 @@
         <v>181.4</v>
       </c>
       <c r="M73">
-        <v>198.6481452</v>
+        <v>201.4460064</v>
       </c>
       <c r="N73">
-        <v>-17.24814519999998</v>
+        <v>-20.04600639999998</v>
       </c>
       <c r="O73">
-        <v>-3.277147587999997</v>
+        <v>-3.808741215999996</v>
       </c>
       <c r="P73">
-        <v>-13.97099761199999</v>
+        <v>-16.23726518399998</v>
       </c>
       <c r="Q73">
-        <v>10.42900238800002</v>
+        <v>8.162734816000022</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1322424633605103</v>
+        <v>0.1353296941948143</v>
       </c>
       <c r="T73">
-        <v>1.684924506168789</v>
+        <v>1.745100381389103</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.173502752644881</v>
+        <v>0.1710929921914799</v>
       </c>
       <c r="W73">
-        <v>0.1213297959117315</v>
+        <v>0.1216835487462908</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9131723823414789</v>
+        <v>0.9004894325867361</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1255044694718774</v>
+        <v>0.1265144694718774</v>
       </c>
       <c r="C74">
-        <v>-115.9626450578828</v>
+        <v>-142.7147753371719</v>
       </c>
       <c r="D74">
-        <v>990.7853549421171</v>
+        <v>983.0922246628279</v>
       </c>
       <c r="E74">
-        <v>1359.148</v>
+        <v>1378.207</v>
       </c>
       <c r="F74">
-        <v>1372.248</v>
+        <v>1391.307</v>
       </c>
       <c r="G74">
         <v>265.5</v>
@@ -7355,37 +7355,37 @@
         <v>181.4</v>
       </c>
       <c r="M74">
-        <v>201.4460064</v>
+        <v>204.2438676</v>
       </c>
       <c r="N74">
-        <v>-20.04600639999998</v>
+        <v>-22.84386759999998</v>
       </c>
       <c r="O74">
-        <v>-3.808741215999996</v>
+        <v>-4.340334843999996</v>
       </c>
       <c r="P74">
-        <v>-16.23726518399998</v>
+        <v>-18.50353275599998</v>
       </c>
       <c r="Q74">
-        <v>8.162734816000022</v>
+        <v>5.896467244000021</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1353296941948143</v>
+        <v>0.1386456087946222</v>
       </c>
       <c r="T74">
-        <v>1.745100381389103</v>
+        <v>1.809733728847958</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1710929921914799</v>
+        <v>0.1687492525724185</v>
       </c>
       <c r="W74">
-        <v>0.1216835487462908</v>
+        <v>0.122027609722369</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9004894325867361</v>
+        <v>0.8881539609074658</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1265144694718774</v>
+        <v>0.1275244694718774</v>
       </c>
       <c r="C75">
-        <v>-142.7147753371719</v>
+        <v>-169.3483567355988</v>
       </c>
       <c r="D75">
-        <v>983.0922246628279</v>
+        <v>975.5176432644013</v>
       </c>
       <c r="E75">
-        <v>1378.207</v>
+        <v>1397.266</v>
       </c>
       <c r="F75">
-        <v>1391.307</v>
+        <v>1410.366</v>
       </c>
       <c r="G75">
         <v>265.5</v>
@@ -7437,37 +7437,37 @@
         <v>181.4</v>
       </c>
       <c r="M75">
-        <v>204.2438676</v>
+        <v>207.0417288</v>
       </c>
       <c r="N75">
-        <v>-22.84386759999998</v>
+        <v>-25.64172880000001</v>
       </c>
       <c r="O75">
-        <v>-4.340334843999996</v>
+        <v>-4.871928472000002</v>
       </c>
       <c r="P75">
-        <v>-18.50353275599998</v>
+        <v>-20.76980032800001</v>
       </c>
       <c r="Q75">
-        <v>5.896467244000021</v>
+        <v>3.630199671999996</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1386456087946222</v>
+        <v>0.1422165937482616</v>
       </c>
       <c r="T75">
-        <v>1.809733728847958</v>
+        <v>1.879338872265188</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1687492525724185</v>
+        <v>0.1664688572673858</v>
       </c>
       <c r="W75">
-        <v>0.122027609722369</v>
+        <v>0.1223623717531478</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8881539609074658</v>
+        <v>0.8761518803546621</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1275244694718774</v>
+        <v>0.1285344694718774</v>
       </c>
       <c r="C76">
-        <v>-169.3483567355988</v>
+        <v>-195.8661085069291</v>
       </c>
       <c r="D76">
-        <v>975.5176432644013</v>
+        <v>968.0588914930709</v>
       </c>
       <c r="E76">
-        <v>1397.266</v>
+        <v>1416.325</v>
       </c>
       <c r="F76">
-        <v>1410.366</v>
+        <v>1429.425</v>
       </c>
       <c r="G76">
         <v>265.5</v>
@@ -7519,37 +7519,37 @@
         <v>181.4</v>
       </c>
       <c r="M76">
-        <v>207.0417288</v>
+        <v>209.83959</v>
       </c>
       <c r="N76">
-        <v>-25.64172880000001</v>
+        <v>-28.43959000000001</v>
       </c>
       <c r="O76">
-        <v>-4.871928472000002</v>
+        <v>-5.403522100000002</v>
       </c>
       <c r="P76">
-        <v>-20.76980032800001</v>
+        <v>-23.03606790000001</v>
       </c>
       <c r="Q76">
-        <v>3.630199671999996</v>
+        <v>1.3639321</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1422165937482616</v>
+        <v>0.146073257498192</v>
       </c>
       <c r="T76">
-        <v>1.879338872265188</v>
+        <v>1.954512427155795</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1664688572673858</v>
+        <v>0.1642492725038207</v>
       </c>
       <c r="W76">
-        <v>0.1223623717531478</v>
+        <v>0.1226882067964391</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8761518803546621</v>
+        <v>0.8644698552832666</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1285344694718774</v>
+        <v>0.1295444694718774</v>
       </c>
       <c r="C77">
-        <v>-195.8661085069291</v>
+        <v>-222.2706673709479</v>
       </c>
       <c r="D77">
-        <v>968.0588914930709</v>
+        <v>960.713332629052</v>
       </c>
       <c r="E77">
-        <v>1416.325</v>
+        <v>1435.384</v>
       </c>
       <c r="F77">
-        <v>1429.425</v>
+        <v>1448.484</v>
       </c>
       <c r="G77">
         <v>265.5</v>
@@ -7601,37 +7601,37 @@
         <v>181.4</v>
       </c>
       <c r="M77">
-        <v>209.83959</v>
+        <v>212.6374512</v>
       </c>
       <c r="N77">
-        <v>-28.43959000000001</v>
+        <v>-31.23745120000001</v>
       </c>
       <c r="O77">
-        <v>-5.403522100000002</v>
+        <v>-5.935115728000002</v>
       </c>
       <c r="P77">
-        <v>-23.03606790000001</v>
+        <v>-25.30233547200001</v>
       </c>
       <c r="Q77">
-        <v>1.3639321</v>
+        <v>-0.9023354720000007</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.146073257498192</v>
+        <v>0.15025130989395</v>
       </c>
       <c r="T77">
-        <v>1.954512427155795</v>
+        <v>2.035950444953954</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1642492725038207</v>
+        <v>0.1620880978656125</v>
       </c>
       <c r="W77">
-        <v>0.1226882067964391</v>
+        <v>0.1230054672333281</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8644698552832666</v>
+        <v>0.8530952519242763</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1295444694718774</v>
+        <v>0.1305544694718773</v>
       </c>
       <c r="C78">
-        <v>-222.2706673709479</v>
+        <v>-248.564590621186</v>
       </c>
       <c r="D78">
-        <v>960.713332629052</v>
+        <v>953.4784093788139</v>
       </c>
       <c r="E78">
-        <v>1435.384</v>
+        <v>1454.443</v>
       </c>
       <c r="F78">
-        <v>1448.484</v>
+        <v>1467.543</v>
       </c>
       <c r="G78">
         <v>265.5</v>
@@ -7683,37 +7683,37 @@
         <v>181.4</v>
       </c>
       <c r="M78">
-        <v>212.6374512</v>
+        <v>215.4353124</v>
       </c>
       <c r="N78">
-        <v>-31.23745120000001</v>
+        <v>-34.03531240000001</v>
       </c>
       <c r="O78">
-        <v>-5.935115728000002</v>
+        <v>-6.466709356000002</v>
       </c>
       <c r="P78">
-        <v>-25.30233547200001</v>
+        <v>-27.56860304400001</v>
       </c>
       <c r="Q78">
-        <v>-0.9023354720000007</v>
+        <v>-3.168603044000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.15025130989395</v>
+        <v>0.154792671193687</v>
       </c>
       <c r="T78">
-        <v>2.035950444953954</v>
+        <v>2.124470029517169</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1620880978656125</v>
+        <v>0.1599830576335916</v>
       </c>
       <c r="W78">
-        <v>0.1230054672333281</v>
+        <v>0.1233144871393888</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8530952519242763</v>
+        <v>0.8420160928083765</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1305544694718773</v>
+        <v>0.1315644694718774</v>
       </c>
       <c r="C79">
-        <v>-248.564590621186</v>
+        <v>-274.7503590932761</v>
       </c>
       <c r="D79">
-        <v>953.4784093788139</v>
+        <v>946.3516409067238</v>
       </c>
       <c r="E79">
-        <v>1454.443</v>
+        <v>1473.502</v>
       </c>
       <c r="F79">
-        <v>1467.543</v>
+        <v>1486.602</v>
       </c>
       <c r="G79">
         <v>265.5</v>
@@ -7765,37 +7765,37 @@
         <v>181.4</v>
       </c>
       <c r="M79">
-        <v>215.4353124</v>
+        <v>218.2331736</v>
       </c>
       <c r="N79">
-        <v>-34.03531240000001</v>
+        <v>-36.83317359999998</v>
       </c>
       <c r="O79">
-        <v>-6.466709356000002</v>
+        <v>-6.998302983999997</v>
       </c>
       <c r="P79">
-        <v>-27.56860304400001</v>
+        <v>-29.83487061599998</v>
       </c>
       <c r="Q79">
-        <v>-3.168603044000001</v>
+        <v>-5.434870615999976</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.154792671193687</v>
+        <v>0.1597468835206728</v>
       </c>
       <c r="T79">
-        <v>2.124470029517169</v>
+        <v>2.221036849040677</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1599830576335916</v>
+        <v>0.1579319927921353</v>
       </c>
       <c r="W79">
-        <v>0.1233144871393888</v>
+        <v>0.1236155834581146</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8420160928083765</v>
+        <v>0.8312210146954487</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1315644694718774</v>
+        <v>0.1325744694718773</v>
       </c>
       <c r="C80">
-        <v>-274.7503590932761</v>
+        <v>-300.8303800011727</v>
       </c>
       <c r="D80">
-        <v>946.3516409067238</v>
+        <v>939.3306199988274</v>
       </c>
       <c r="E80">
-        <v>1473.502</v>
+        <v>1492.561</v>
       </c>
       <c r="F80">
-        <v>1486.602</v>
+        <v>1505.661</v>
       </c>
       <c r="G80">
         <v>265.5</v>
@@ -7847,37 +7847,37 @@
         <v>181.4</v>
       </c>
       <c r="M80">
-        <v>218.2331736</v>
+        <v>221.0310348</v>
       </c>
       <c r="N80">
-        <v>-36.83317359999998</v>
+        <v>-39.63103480000004</v>
       </c>
       <c r="O80">
-        <v>-6.998302983999997</v>
+        <v>-7.529896612000007</v>
       </c>
       <c r="P80">
-        <v>-29.83487061599998</v>
+        <v>-32.10113818800003</v>
       </c>
       <c r="Q80">
-        <v>-5.434870615999976</v>
+        <v>-7.701138188000023</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1597468835206728</v>
+        <v>0.1651729255930857</v>
       </c>
       <c r="T80">
-        <v>2.221036849040677</v>
+        <v>2.326800508518804</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1579319927921353</v>
+        <v>0.1559328536428677</v>
       </c>
       <c r="W80">
-        <v>0.1236155834581146</v>
+        <v>0.123909057085227</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8312210146954487</v>
+        <v>0.8206992296993036</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1325744694718773</v>
+        <v>0.1335844694718774</v>
       </c>
       <c r="C81">
-        <v>-300.8303800011727</v>
+        <v>-326.8069896480511</v>
       </c>
       <c r="D81">
-        <v>939.3306199988274</v>
+        <v>932.413010351949</v>
       </c>
       <c r="E81">
-        <v>1492.561</v>
+        <v>1511.62</v>
       </c>
       <c r="F81">
-        <v>1505.661</v>
+        <v>1524.72</v>
       </c>
       <c r="G81">
         <v>265.5</v>
@@ -7929,37 +7929,37 @@
         <v>181.4</v>
       </c>
       <c r="M81">
-        <v>221.0310348</v>
+        <v>223.828896</v>
       </c>
       <c r="N81">
-        <v>-39.63103480000004</v>
+        <v>-42.42889600000001</v>
       </c>
       <c r="O81">
-        <v>-7.529896612000007</v>
+        <v>-8.061490240000001</v>
       </c>
       <c r="P81">
-        <v>-32.10113818800003</v>
+        <v>-34.36740576000001</v>
       </c>
       <c r="Q81">
-        <v>-7.701138188000023</v>
+        <v>-9.967405760000005</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1651729255930857</v>
+        <v>0.17114157187274</v>
       </c>
       <c r="T81">
-        <v>2.326800508518804</v>
+        <v>2.443140533944745</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1559328536428677</v>
+        <v>0.1539836929723319</v>
       </c>
       <c r="W81">
-        <v>0.123909057085227</v>
+        <v>0.1241951938716617</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8206992296993036</v>
+        <v>0.8104404893280625</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1335844694718774</v>
+        <v>0.1345944694718774</v>
       </c>
       <c r="C82">
-        <v>-326.8069896480511</v>
+        <v>-352.6824560182981</v>
       </c>
       <c r="D82">
-        <v>932.413010351949</v>
+        <v>925.596543981702</v>
       </c>
       <c r="E82">
-        <v>1511.62</v>
+        <v>1530.679</v>
       </c>
       <c r="F82">
-        <v>1524.72</v>
+        <v>1543.779</v>
       </c>
       <c r="G82">
         <v>265.5</v>
@@ -8011,37 +8011,37 @@
         <v>181.4</v>
       </c>
       <c r="M82">
-        <v>223.828896</v>
+        <v>226.6267572</v>
       </c>
       <c r="N82">
-        <v>-42.42889600000001</v>
+        <v>-45.22675720000001</v>
       </c>
       <c r="O82">
-        <v>-8.061490240000001</v>
+        <v>-8.593083868000003</v>
       </c>
       <c r="P82">
-        <v>-34.36740576000001</v>
+        <v>-36.63367333200001</v>
       </c>
       <c r="Q82">
-        <v>-9.967405760000005</v>
+        <v>-12.233673332</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.17114157187274</v>
+        <v>0.1777384967081474</v>
       </c>
       <c r="T82">
-        <v>2.443140533944745</v>
+        <v>2.571726877836574</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1539836929723319</v>
+        <v>0.1520826597257599</v>
       </c>
       <c r="W82">
-        <v>0.1241951938716617</v>
+        <v>0.1244742655522585</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8104404893280625</v>
+        <v>0.8004350511882098</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1345944694718774</v>
+        <v>0.1808316066818905</v>
       </c>
       <c r="C83">
-        <v>-352.6824560182981</v>
+        <v>-603.8373298368483</v>
       </c>
       <c r="D83">
-        <v>925.596543981702</v>
+        <v>693.5006701631517</v>
       </c>
       <c r="E83">
-        <v>1530.679</v>
+        <v>1549.738</v>
       </c>
       <c r="F83">
-        <v>1543.779</v>
+        <v>1562.838</v>
       </c>
       <c r="G83">
         <v>265.5</v>
@@ -8093,45 +8093,45 @@
         <v>181.4</v>
       </c>
       <c r="M83">
-        <v>226.6267572</v>
+        <v>313.8178704</v>
       </c>
       <c r="N83">
-        <v>-45.22675720000001</v>
+        <v>-132.4178704</v>
       </c>
       <c r="O83">
-        <v>-8.593083868000003</v>
+        <v>-25.159395376</v>
       </c>
       <c r="P83">
-        <v>-36.63367333200001</v>
+        <v>-107.258475024</v>
       </c>
       <c r="Q83">
-        <v>-12.233673332</v>
+        <v>-82.858475024</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1777384967081474</v>
+        <v>0.1903302865808953</v>
       </c>
       <c r="T83">
-        <v>2.571726877836574</v>
+        <v>2.817164299542595</v>
       </c>
       <c r="U83">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1520826597257599</v>
+        <v>0.1098280348281912</v>
       </c>
       <c r="W83">
-        <v>0.1244742655522585</v>
+        <v>0.1787465306064992</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8004350511882098</v>
+        <v>0.5780422885694275</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1808316066818905</v>
+        <v>0.1823816066818905</v>
       </c>
       <c r="C84">
-        <v>-603.8373298368483</v>
+        <v>-628.6772629590505</v>
       </c>
       <c r="D84">
-        <v>693.5006701631517</v>
+        <v>687.7197370409494</v>
       </c>
       <c r="E84">
-        <v>1549.738</v>
+        <v>1568.797</v>
       </c>
       <c r="F84">
-        <v>1562.838</v>
+        <v>1581.897</v>
       </c>
       <c r="G84">
         <v>265.5</v>
@@ -8175,37 +8175,37 @@
         <v>181.4</v>
       </c>
       <c r="M84">
-        <v>313.8178704</v>
+        <v>317.6449176</v>
       </c>
       <c r="N84">
-        <v>-132.4178704</v>
+        <v>-136.2449176</v>
       </c>
       <c r="O84">
-        <v>-25.159395376</v>
+        <v>-25.886534344</v>
       </c>
       <c r="P84">
-        <v>-107.258475024</v>
+        <v>-110.358383256</v>
       </c>
       <c r="Q84">
-        <v>-82.858475024</v>
+        <v>-85.95838325599998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1903302865808953</v>
+        <v>0.1988320681444774</v>
       </c>
       <c r="T84">
-        <v>2.817164299542595</v>
+        <v>2.982879846574512</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1098280348281912</v>
+        <v>0.1085048054929118</v>
       </c>
       <c r="W84">
-        <v>0.1787465306064992</v>
+        <v>0.1790122350570233</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5780422885694275</v>
+        <v>0.5710779236469044</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1823816066818905</v>
+        <v>0.1839316066818905</v>
       </c>
       <c r="C85">
-        <v>-628.6772629590505</v>
+        <v>-653.4216145941771</v>
       </c>
       <c r="D85">
-        <v>687.7197370409494</v>
+        <v>682.0343854058231</v>
       </c>
       <c r="E85">
-        <v>1568.797</v>
+        <v>1587.856</v>
       </c>
       <c r="F85">
-        <v>1581.897</v>
+        <v>1600.956</v>
       </c>
       <c r="G85">
         <v>265.5</v>
@@ -8257,37 +8257,37 @@
         <v>181.4</v>
       </c>
       <c r="M85">
-        <v>317.6449176</v>
+        <v>321.4719648</v>
       </c>
       <c r="N85">
-        <v>-136.2449176</v>
+        <v>-140.0719648</v>
       </c>
       <c r="O85">
-        <v>-25.886534344</v>
+        <v>-26.613673312</v>
       </c>
       <c r="P85">
-        <v>-110.358383256</v>
+        <v>-113.458291488</v>
       </c>
       <c r="Q85">
-        <v>-85.95838325599998</v>
+        <v>-89.05829148800001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1988320681444774</v>
+        <v>0.2083965724035073</v>
       </c>
       <c r="T85">
-        <v>2.982879846574512</v>
+        <v>3.16930983698542</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1085048054929118</v>
+        <v>0.1072130816179962</v>
       </c>
       <c r="W85">
-        <v>0.1790122350570233</v>
+        <v>0.1792716132111064</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5710779236469044</v>
+        <v>0.5642793769368221</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1839316066818905</v>
+        <v>0.1854816066818905</v>
       </c>
       <c r="C86">
-        <v>-653.4216145941768</v>
+        <v>-678.0727358110589</v>
       </c>
       <c r="D86">
-        <v>682.0343854058231</v>
+        <v>676.442264188941</v>
       </c>
       <c r="E86">
-        <v>1587.856</v>
+        <v>1606.915</v>
       </c>
       <c r="F86">
-        <v>1600.956</v>
+        <v>1620.015</v>
       </c>
       <c r="G86">
         <v>265.5</v>
@@ -8339,37 +8339,37 @@
         <v>181.4</v>
       </c>
       <c r="M86">
-        <v>321.4719648</v>
+        <v>325.299012</v>
       </c>
       <c r="N86">
-        <v>-140.0719648</v>
+        <v>-143.899012</v>
       </c>
       <c r="O86">
-        <v>-26.61367331199999</v>
+        <v>-27.34081228</v>
       </c>
       <c r="P86">
-        <v>-113.458291488</v>
+        <v>-116.55819972</v>
       </c>
       <c r="Q86">
-        <v>-89.05829148799997</v>
+        <v>-92.15819972</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2083965724035071</v>
+        <v>0.2192363438970743</v>
       </c>
       <c r="T86">
-        <v>3.169309836985418</v>
+        <v>3.380597159451113</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1072130816179962</v>
+        <v>0.1059517512460198</v>
       </c>
       <c r="W86">
-        <v>0.1792716132111064</v>
+        <v>0.1795248883497992</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5642793769368222</v>
+        <v>0.5576407960316829</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1854816066818905</v>
+        <v>0.1870316066818905</v>
       </c>
       <c r="C87">
-        <v>-678.0727358110589</v>
+        <v>-702.6329011982772</v>
       </c>
       <c r="D87">
-        <v>676.442264188941</v>
+        <v>670.9410988017227</v>
       </c>
       <c r="E87">
-        <v>1606.915</v>
+        <v>1625.974</v>
       </c>
       <c r="F87">
-        <v>1620.015</v>
+        <v>1639.074</v>
       </c>
       <c r="G87">
         <v>265.5</v>
@@ -8421,37 +8421,37 @@
         <v>181.4</v>
       </c>
       <c r="M87">
-        <v>325.299012</v>
+        <v>329.1260592</v>
       </c>
       <c r="N87">
-        <v>-143.899012</v>
+        <v>-147.7260592</v>
       </c>
       <c r="O87">
-        <v>-27.34081228</v>
+        <v>-28.067951248</v>
       </c>
       <c r="P87">
-        <v>-116.55819972</v>
+        <v>-119.658107952</v>
       </c>
       <c r="Q87">
-        <v>-92.15819972</v>
+        <v>-95.25810795199997</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2192363438970743</v>
+        <v>0.2316246541754368</v>
       </c>
       <c r="T87">
-        <v>3.380597159451113</v>
+        <v>3.622068385126192</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1059517512460198</v>
+        <v>0.1047197541385079</v>
       </c>
       <c r="W87">
-        <v>0.1795248883497992</v>
+        <v>0.1797722733689876</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5576407960316829</v>
+        <v>0.551156600728989</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1870316066818905</v>
+        <v>0.1885816066818905</v>
       </c>
       <c r="C88">
-        <v>-702.6329011982772</v>
+        <v>-727.1043119489524</v>
       </c>
       <c r="D88">
-        <v>670.9410988017227</v>
+        <v>665.5286880510474</v>
       </c>
       <c r="E88">
-        <v>1625.974</v>
+        <v>1645.033</v>
       </c>
       <c r="F88">
-        <v>1639.074</v>
+        <v>1658.133</v>
       </c>
       <c r="G88">
         <v>265.5</v>
@@ -8503,37 +8503,37 @@
         <v>181.4</v>
       </c>
       <c r="M88">
-        <v>329.1260592</v>
+        <v>332.9531064</v>
       </c>
       <c r="N88">
-        <v>-147.7260592</v>
+        <v>-151.5531064</v>
       </c>
       <c r="O88">
-        <v>-28.067951248</v>
+        <v>-28.79509021599999</v>
       </c>
       <c r="P88">
-        <v>-119.658107952</v>
+        <v>-122.758016184</v>
       </c>
       <c r="Q88">
-        <v>-95.25810795199997</v>
+        <v>-98.35801618399996</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2316246541754368</v>
+        <v>0.245918858342778</v>
       </c>
       <c r="T88">
-        <v>3.622068385126192</v>
+        <v>3.900689030135899</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1047197541385079</v>
+        <v>0.1035160788035825</v>
       </c>
       <c r="W88">
-        <v>0.1797722733689876</v>
+        <v>0.1800139713762406</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.551156600728989</v>
+        <v>0.5448214673872765</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1885816066818905</v>
+        <v>0.1901316066818905</v>
       </c>
       <c r="C89">
-        <v>-727.1043119489524</v>
+        <v>-751.4890987974215</v>
       </c>
       <c r="D89">
-        <v>665.5286880510474</v>
+        <v>660.2029012025782</v>
       </c>
       <c r="E89">
-        <v>1645.033</v>
+        <v>1664.092</v>
       </c>
       <c r="F89">
-        <v>1658.133</v>
+        <v>1677.192</v>
       </c>
       <c r="G89">
         <v>265.5</v>
@@ -8585,37 +8585,37 @@
         <v>181.4</v>
       </c>
       <c r="M89">
-        <v>332.9531064</v>
+        <v>336.7801535999999</v>
       </c>
       <c r="N89">
-        <v>-151.5531064</v>
+        <v>-155.3801535999999</v>
       </c>
       <c r="O89">
-        <v>-28.79509021599999</v>
+        <v>-29.52222918399999</v>
       </c>
       <c r="P89">
-        <v>-122.758016184</v>
+        <v>-125.8579244159999</v>
       </c>
       <c r="Q89">
-        <v>-98.35801618399996</v>
+        <v>-101.4579244159999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.245918858342778</v>
+        <v>0.2625954298713429</v>
       </c>
       <c r="T89">
-        <v>3.900689030135899</v>
+        <v>4.225746449313891</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1035160788035825</v>
+        <v>0.1023397597262691</v>
       </c>
       <c r="W89">
-        <v>0.1800139713762406</v>
+        <v>0.1802501762469652</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5448214673872765</v>
+        <v>0.5386303143487848</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1901316066818905</v>
+        <v>0.1916816066818905</v>
       </c>
       <c r="C90">
-        <v>-751.4890987974215</v>
+        <v>-775.7893248160343</v>
       </c>
       <c r="D90">
-        <v>660.2029012025782</v>
+        <v>654.9616751839657</v>
       </c>
       <c r="E90">
-        <v>1664.092</v>
+        <v>1683.151</v>
       </c>
       <c r="F90">
-        <v>1677.192</v>
+        <v>1696.251</v>
       </c>
       <c r="G90">
         <v>265.5</v>
@@ -8667,37 +8667,37 @@
         <v>181.4</v>
       </c>
       <c r="M90">
-        <v>336.7801535999999</v>
+        <v>340.6072008</v>
       </c>
       <c r="N90">
-        <v>-155.3801535999999</v>
+        <v>-159.2072008</v>
       </c>
       <c r="O90">
-        <v>-29.52222918399999</v>
+        <v>-30.249368152</v>
       </c>
       <c r="P90">
-        <v>-125.8579244159999</v>
+        <v>-128.957832648</v>
       </c>
       <c r="Q90">
-        <v>-101.4579244159999</v>
+        <v>-104.557832648</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2625954298713429</v>
+        <v>0.2823041053141923</v>
       </c>
       <c r="T90">
-        <v>4.225746449313891</v>
+        <v>4.609905217433336</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1023397597262691</v>
+        <v>0.1011898747855245</v>
       </c>
       <c r="W90">
-        <v>0.1802501762469652</v>
+        <v>0.1804810731430667</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5386303143487848</v>
+        <v>0.5325782883448658</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1916816066818905</v>
+        <v>0.1932316066818905</v>
       </c>
       <c r="C91">
-        <v>-775.7893248160343</v>
+        <v>-800.0069880797754</v>
       </c>
       <c r="D91">
-        <v>654.9616751839657</v>
+        <v>649.8030119202245</v>
       </c>
       <c r="E91">
-        <v>1683.151</v>
+        <v>1702.21</v>
       </c>
       <c r="F91">
-        <v>1696.251</v>
+        <v>1715.31</v>
       </c>
       <c r="G91">
         <v>265.5</v>
@@ -8749,37 +8749,37 @@
         <v>181.4</v>
       </c>
       <c r="M91">
-        <v>340.6072008</v>
+        <v>344.434248</v>
       </c>
       <c r="N91">
-        <v>-159.2072008</v>
+        <v>-163.034248</v>
       </c>
       <c r="O91">
-        <v>-30.249368152</v>
+        <v>-30.97650712</v>
       </c>
       <c r="P91">
-        <v>-128.957832648</v>
+        <v>-132.05774088</v>
       </c>
       <c r="Q91">
-        <v>-104.557832648</v>
+        <v>-107.65774088</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2823041053141923</v>
+        <v>0.3059545158456115</v>
       </c>
       <c r="T91">
-        <v>4.609905217433336</v>
+        <v>5.070895739176669</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1011898747855245</v>
+        <v>0.1000655428434631</v>
       </c>
       <c r="W91">
-        <v>0.1804810731430667</v>
+        <v>0.1807068389970326</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5325782883448658</v>
+        <v>0.5266607518077007</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1932316066818905</v>
+        <v>0.1947816066818905</v>
       </c>
       <c r="C92">
-        <v>-800.0069880797754</v>
+        <v>-824.1440242059517</v>
       </c>
       <c r="D92">
-        <v>649.8030119202245</v>
+        <v>644.7249757940482</v>
       </c>
       <c r="E92">
-        <v>1702.21</v>
+        <v>1721.269</v>
       </c>
       <c r="F92">
-        <v>1715.31</v>
+        <v>1734.369</v>
       </c>
       <c r="G92">
         <v>265.5</v>
@@ -8831,37 +8831,37 @@
         <v>181.4</v>
       </c>
       <c r="M92">
-        <v>344.434248</v>
+        <v>348.2612952</v>
       </c>
       <c r="N92">
-        <v>-163.034248</v>
+        <v>-166.8612952</v>
       </c>
       <c r="O92">
-        <v>-30.97650712</v>
+        <v>-31.703646088</v>
       </c>
       <c r="P92">
-        <v>-132.05774088</v>
+        <v>-135.157649112</v>
       </c>
       <c r="Q92">
-        <v>-107.65774088</v>
+        <v>-110.757649112</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3059545158456115</v>
+        <v>0.3348605731617906</v>
       </c>
       <c r="T92">
-        <v>5.070895739176669</v>
+        <v>5.634328599085189</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1000655428434631</v>
+        <v>0.09896592149353496</v>
       </c>
       <c r="W92">
-        <v>0.1807068389970326</v>
+        <v>0.1809276429640982</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5266607518077007</v>
+        <v>0.520873271018605</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1947816066818905</v>
+        <v>0.1963316066818905</v>
       </c>
       <c r="C93">
-        <v>-824.1440242059517</v>
+        <v>-848.2023087757174</v>
       </c>
       <c r="D93">
-        <v>644.7249757940482</v>
+        <v>639.7256912242825</v>
       </c>
       <c r="E93">
-        <v>1721.269</v>
+        <v>1740.328</v>
       </c>
       <c r="F93">
-        <v>1734.369</v>
+        <v>1753.428</v>
       </c>
       <c r="G93">
         <v>265.5</v>
@@ -8913,37 +8913,37 @@
         <v>181.4</v>
       </c>
       <c r="M93">
-        <v>348.2612952</v>
+        <v>352.0883424</v>
       </c>
       <c r="N93">
-        <v>-166.8612952</v>
+        <v>-170.6883424</v>
       </c>
       <c r="O93">
-        <v>-31.703646088</v>
+        <v>-32.430785056</v>
       </c>
       <c r="P93">
-        <v>-135.157649112</v>
+        <v>-138.257557344</v>
       </c>
       <c r="Q93">
-        <v>-110.757649112</v>
+        <v>-113.857557344</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3348605731617906</v>
+        <v>0.3709931448070145</v>
       </c>
       <c r="T93">
-        <v>5.634328599085189</v>
+        <v>6.338619673970839</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.09896592149353496</v>
+        <v>0.09789020495556175</v>
       </c>
       <c r="W93">
-        <v>0.1809276429640982</v>
+        <v>0.1811436468449232</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.520873271018605</v>
+        <v>0.5152116050292723</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1963316066818905</v>
+        <v>0.1978816066818905</v>
       </c>
       <c r="C94">
-        <v>-848.2023087757174</v>
+        <v>-872.1836596438063</v>
       </c>
       <c r="D94">
-        <v>639.7256912242825</v>
+        <v>634.8033403561935</v>
       </c>
       <c r="E94">
-        <v>1740.328</v>
+        <v>1759.387</v>
       </c>
       <c r="F94">
-        <v>1753.428</v>
+        <v>1772.487</v>
       </c>
       <c r="G94">
         <v>265.5</v>
@@ -8995,37 +8995,37 @@
         <v>181.4</v>
       </c>
       <c r="M94">
-        <v>352.0883424</v>
+        <v>355.9153896</v>
       </c>
       <c r="N94">
-        <v>-170.6883424</v>
+        <v>-174.5153896</v>
       </c>
       <c r="O94">
-        <v>-32.430785056</v>
+        <v>-33.157924024</v>
       </c>
       <c r="P94">
-        <v>-138.257557344</v>
+        <v>-141.357465576</v>
       </c>
       <c r="Q94">
-        <v>-113.857557344</v>
+        <v>-116.957465576</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3709931448070145</v>
+        <v>0.4174493083508738</v>
       </c>
       <c r="T94">
-        <v>6.338619673970839</v>
+        <v>7.244136770252389</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09789020495556175</v>
+        <v>0.09683762210657723</v>
       </c>
       <c r="W94">
-        <v>0.1811436468449232</v>
+        <v>0.1813550054809993</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5152116050292723</v>
+        <v>0.5096716952977749</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1978816066818905</v>
+        <v>0.1994316066818905</v>
       </c>
       <c r="C95">
-        <v>-872.1836596438063</v>
+        <v>-896.0898391424455</v>
       </c>
       <c r="D95">
-        <v>634.8033403561935</v>
+        <v>629.9561608575546</v>
       </c>
       <c r="E95">
-        <v>1759.387</v>
+        <v>1778.446</v>
       </c>
       <c r="F95">
-        <v>1772.487</v>
+        <v>1791.546</v>
       </c>
       <c r="G95">
         <v>265.5</v>
@@ -9077,37 +9077,37 @@
         <v>181.4</v>
       </c>
       <c r="M95">
-        <v>355.9153896</v>
+        <v>359.7424368</v>
       </c>
       <c r="N95">
-        <v>-174.5153896</v>
+        <v>-178.3424368</v>
       </c>
       <c r="O95">
-        <v>-33.157924024</v>
+        <v>-33.885062992</v>
       </c>
       <c r="P95">
-        <v>-141.357465576</v>
+        <v>-144.457373808</v>
       </c>
       <c r="Q95">
-        <v>-116.957465576</v>
+        <v>-120.057373808</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4174493083508738</v>
+        <v>0.4793908597426861</v>
       </c>
       <c r="T95">
-        <v>7.244136770252389</v>
+        <v>8.451492898627789</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09683762210657723</v>
+        <v>0.09580743463735829</v>
       </c>
       <c r="W95">
-        <v>0.1813550054809993</v>
+        <v>0.1815618671248184</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5096716952977749</v>
+        <v>0.5042496559860963</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1994316066818905</v>
+        <v>0.2346137879862796</v>
       </c>
       <c r="C96">
-        <v>-896.0898391424455</v>
+        <v>-1008.203034343276</v>
       </c>
       <c r="D96">
-        <v>629.9561608575546</v>
+        <v>536.9019656567243</v>
       </c>
       <c r="E96">
-        <v>1778.446</v>
+        <v>1797.505</v>
       </c>
       <c r="F96">
-        <v>1791.546</v>
+        <v>1810.605</v>
       </c>
       <c r="G96">
         <v>265.5</v>
@@ -9159,45 +9159,45 @@
         <v>181.4</v>
       </c>
       <c r="M96">
-        <v>359.7424368</v>
+        <v>426.940659</v>
       </c>
       <c r="N96">
-        <v>-178.3424368</v>
+        <v>-245.540659</v>
       </c>
       <c r="O96">
-        <v>-33.885062992</v>
+        <v>-46.65272521000001</v>
       </c>
       <c r="P96">
-        <v>-144.457373808</v>
+        <v>-198.88793379</v>
       </c>
       <c r="Q96">
-        <v>-120.057373808</v>
+        <v>-174.48793379</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4793908597426861</v>
+        <v>0.573752657779006</v>
       </c>
       <c r="T96">
-        <v>8.451492898627789</v>
+        <v>10.29077997787799</v>
       </c>
       <c r="U96">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09580743463735829</v>
+        <v>0.08072784653663075</v>
       </c>
       <c r="W96">
-        <v>0.1815618671248184</v>
+        <v>0.2167643737866625</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.5042496559860963</v>
+        <v>0.4248834028243723</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2346137879862796</v>
+        <v>0.2365137879862796</v>
       </c>
       <c r="C97">
-        <v>-1008.203034343276</v>
+        <v>-1031.511171074582</v>
       </c>
       <c r="D97">
-        <v>536.9019656567243</v>
+        <v>532.6528289254179</v>
       </c>
       <c r="E97">
-        <v>1797.505</v>
+        <v>1816.564</v>
       </c>
       <c r="F97">
-        <v>1810.605</v>
+        <v>1829.664</v>
       </c>
       <c r="G97">
         <v>265.5</v>
@@ -9241,37 +9241,37 @@
         <v>181.4</v>
       </c>
       <c r="M97">
-        <v>426.940659</v>
+        <v>431.4347712</v>
       </c>
       <c r="N97">
-        <v>-245.540659</v>
+        <v>-250.0347712</v>
       </c>
       <c r="O97">
-        <v>-46.65272521000001</v>
+        <v>-47.506606528</v>
       </c>
       <c r="P97">
-        <v>-198.88793379</v>
+        <v>-202.528164672</v>
       </c>
       <c r="Q97">
-        <v>-174.48793379</v>
+        <v>-178.128164672</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.573752657779006</v>
+        <v>0.7057408222237577</v>
       </c>
       <c r="T97">
-        <v>10.29077997787799</v>
+        <v>12.86347497234749</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08072784653663075</v>
+        <v>0.07988693146854085</v>
       </c>
       <c r="W97">
-        <v>0.2167643737866625</v>
+        <v>0.2169626615597181</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4248834028243723</v>
+        <v>0.4204575340449518</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2365137879862796</v>
+        <v>0.2384137879862796</v>
       </c>
       <c r="C98">
-        <v>-1031.511171074582</v>
+        <v>-1054.752579075662</v>
       </c>
       <c r="D98">
-        <v>532.6528289254179</v>
+        <v>528.4704209243373</v>
       </c>
       <c r="E98">
-        <v>1816.564</v>
+        <v>1835.623</v>
       </c>
       <c r="F98">
-        <v>1829.664</v>
+        <v>1848.723</v>
       </c>
       <c r="G98">
         <v>265.5</v>
@@ -9323,37 +9323,37 @@
         <v>181.4</v>
       </c>
       <c r="M98">
-        <v>431.4347711999999</v>
+        <v>435.9288834</v>
       </c>
       <c r="N98">
-        <v>-250.0347711999999</v>
+        <v>-254.5288834</v>
       </c>
       <c r="O98">
-        <v>-47.50660652799999</v>
+        <v>-48.36048784599999</v>
       </c>
       <c r="P98">
-        <v>-202.5281646719999</v>
+        <v>-206.168395554</v>
       </c>
       <c r="Q98">
-        <v>-178.1281646719999</v>
+        <v>-181.768395554</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7057408222237559</v>
+        <v>0.9257210962983414</v>
       </c>
       <c r="T98">
-        <v>12.86347497234745</v>
+        <v>17.15129996312994</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07988693146854087</v>
+        <v>0.07906335485546312</v>
       </c>
       <c r="W98">
-        <v>0.2169626615597181</v>
+        <v>0.2171568609250818</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4204575340449519</v>
+        <v>0.4161229202919111</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2384137879862796</v>
+        <v>0.2403137879862796</v>
       </c>
       <c r="C99">
-        <v>-1054.752579075662</v>
+        <v>-1077.928817969038</v>
       </c>
       <c r="D99">
-        <v>528.4704209243373</v>
+        <v>524.3531820309615</v>
       </c>
       <c r="E99">
-        <v>1835.623</v>
+        <v>1854.682</v>
       </c>
       <c r="F99">
-        <v>1848.723</v>
+        <v>1867.782</v>
       </c>
       <c r="G99">
         <v>265.5</v>
@@ -9405,37 +9405,37 @@
         <v>181.4</v>
       </c>
       <c r="M99">
-        <v>435.9288834</v>
+        <v>440.4229956</v>
       </c>
       <c r="N99">
-        <v>-254.5288834</v>
+        <v>-259.0229955999999</v>
       </c>
       <c r="O99">
-        <v>-48.36048784599999</v>
+        <v>-49.21436916399999</v>
       </c>
       <c r="P99">
-        <v>-206.168395554</v>
+        <v>-209.8086264359999</v>
       </c>
       <c r="Q99">
-        <v>-181.768395554</v>
+        <v>-185.4086264359999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9257210962983414</v>
+        <v>1.365681644447512</v>
       </c>
       <c r="T99">
-        <v>17.15129996312994</v>
+        <v>25.7269499446949</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07906335485546312</v>
+        <v>0.07825658592836654</v>
       </c>
       <c r="W99">
-        <v>0.2171568609250818</v>
+        <v>0.2173470970380912</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4161229202919111</v>
+        <v>0.4118767680440345</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2403137879862796</v>
+        <v>0.2422137879862796</v>
       </c>
       <c r="C100">
-        <v>-1077.928817969038</v>
+        <v>-1101.041399149763</v>
       </c>
       <c r="D100">
-        <v>524.3531820309615</v>
+        <v>520.2996008502367</v>
       </c>
       <c r="E100">
-        <v>1854.682</v>
+        <v>1873.741</v>
       </c>
       <c r="F100">
-        <v>1867.782</v>
+        <v>1886.841</v>
       </c>
       <c r="G100">
         <v>265.5</v>
@@ -9487,37 +9487,37 @@
         <v>181.4</v>
       </c>
       <c r="M100">
-        <v>440.4229956</v>
+        <v>444.9171078</v>
       </c>
       <c r="N100">
-        <v>-259.0229955999999</v>
+        <v>-263.5171078</v>
       </c>
       <c r="O100">
-        <v>-49.21436916399999</v>
+        <v>-50.068250482</v>
       </c>
       <c r="P100">
-        <v>-209.8086264359999</v>
+        <v>-213.448857318</v>
       </c>
       <c r="Q100">
-        <v>-185.4086264359999</v>
+        <v>-189.048857318</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.365681644447512</v>
+        <v>2.685563288895024</v>
       </c>
       <c r="T100">
-        <v>25.7269499446949</v>
+        <v>51.45389988938981</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07825658592836654</v>
+        <v>0.07746611536343355</v>
       </c>
       <c r="W100">
-        <v>0.2173470970380912</v>
+        <v>0.2175334899973024</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4118767680440345</v>
+        <v>0.4077163966496503</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2422137879862796</v>
-      </c>
-      <c r="C101">
-        <v>-1101.041399149763</v>
-      </c>
-      <c r="D101">
-        <v>520.2996008502367</v>
-      </c>
-      <c r="E101">
-        <v>1873.741</v>
-      </c>
-      <c r="F101">
-        <v>1886.841</v>
-      </c>
-      <c r="G101">
-        <v>265.5</v>
-      </c>
-      <c r="H101">
-        <v>1892.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>205.8</v>
-      </c>
-      <c r="K101">
-        <v>24.40000000000001</v>
-      </c>
-      <c r="L101">
-        <v>181.4</v>
-      </c>
-      <c r="M101">
-        <v>444.9171078</v>
-      </c>
-      <c r="N101">
-        <v>-263.5171078</v>
-      </c>
-      <c r="O101">
-        <v>-50.068250482</v>
-      </c>
-      <c r="P101">
-        <v>-213.448857318</v>
-      </c>
-      <c r="Q101">
-        <v>-189.048857318</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.685563288895024</v>
-      </c>
-      <c r="T101">
-        <v>51.45389988938981</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07746611536343355</v>
-      </c>
-      <c r="W101">
-        <v>0.2175334899973024</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4077163966496503</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
